--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46048</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45901</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45700</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45110</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>45502</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45833</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45973</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45278</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>46267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>46238</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45810</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45919</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45988</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>46259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45945</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>44697</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44532</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45901</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46057</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46108</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46248</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45979</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45407</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45929</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>46052</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>46058</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44543</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45973</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45159</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45938</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45918</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45393</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45912</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46267</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44846</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>46003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46036</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46057</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46031</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45415</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45891</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44473</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44817</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44830</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45362</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46142</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44519</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>45593</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44522</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45966</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>46167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46008</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44923</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45600</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46079</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45522</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45943</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46238</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45988</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45210</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>45968</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45987</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46010</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>46057</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45895</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46272</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13882,10 +13882,10 @@
         <v>7</v>
       </c>
       <c r="T108" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>46238</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>45834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44828</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44971</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44472</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>46002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45769</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>46134</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45448</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45210</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45365</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45173</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45902</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>46142</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45225</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46202</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45755</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45432</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45462</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>46283</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45799</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46121</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45078</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45182</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45547</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45937</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44830</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45511</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>46057</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45511</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>44461</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>46212</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46254</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46236</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45786</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45145</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45426</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44830</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45502</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45985</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45992</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46195</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>46127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45343</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45810</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45817</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45841</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44525</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44706</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45496</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44473</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45968</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45404</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>46177</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46196</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46121</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44874</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46265</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45575</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45575</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45833</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45902</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46265</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44516</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>44532</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45432</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45181</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45502</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>45153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45512</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44881</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45989</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>46002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44873</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>46177</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>46058</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46189</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45792</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46248</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45511</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46261</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46223</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>46266</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>46233</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45786</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45817</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45853</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45770</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45572</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45684</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44575</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45903</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44662</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44754</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>44810</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44546</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44471</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44651</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44519</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44477</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>44817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44504</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>44459</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44467</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>44538</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44865</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44462</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>44459</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44697</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44477</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>44461</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44501</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44705</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44484</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44477</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>44732</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>44539</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44536</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44680</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44607</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44882</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44636</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44816</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44547</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45534</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45456</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44476</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45054</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45097</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44558</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45307</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44526</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45307</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44526</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45246</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45357</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45491</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45247</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45210</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45477</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45477</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44568</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45210</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>45488</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45545</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45335</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45253</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45693</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44839</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45548</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45322</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45322</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45322</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45679</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45491</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45015</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44755</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45597</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45335</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>44873</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45310</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45310</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44820</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>45566</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45175</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45299</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44473</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44505</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45646</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45201</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45336</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45299</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45665</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45233</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45310</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44888</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45700</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45722</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45722</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45560</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45901</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45512</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>45630</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>45159</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45274</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45484</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45477</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>45322</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45887</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45898</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45911</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45691</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45911</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45665</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45589</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>46079</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46043</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45919</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45420</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45929</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45929</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45931</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45931</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45933</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45638</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45254</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45709</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46148</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45356</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44904</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>46149</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>46149</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45212</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>46148</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>46149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45950</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45950</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45950</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45209</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45950</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45953</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45952</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45952</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45141</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>44844</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>46153</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44896</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>45077</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44678</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45968</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>46154</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45973</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45973</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45076</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>44754</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45974</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45485</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>45980</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45246</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45124</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>44859</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45988</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45988</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45988</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45550</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45992</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45992</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45992</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44558</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44495</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45996</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44651</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45456</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45456</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>46001</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45327</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45110</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>46013</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>46168</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45072</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>46014</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45638</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45665</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45700</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45584</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44755</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>44873</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>46029</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>46029</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45240</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45240</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46029</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46030</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>46052</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>46035</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46174</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>46174</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>46031</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>46174</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>46041</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>46041</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>46038</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>46038</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45247</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>46038</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>46038</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46038</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>46038</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>46038</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46043</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>46043</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>46043</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>46042</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>44844</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45770</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>46044</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>46174</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45925</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45588</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45204</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45507</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>46057</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45328</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>46030</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>46062</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>46062</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46062</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46062</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44978</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46062</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46177</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>46066</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46071</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>46071</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>46073</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44874</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>46078</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45104</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45424,7 +45424,7 @@
         <v>46085</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45113</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45114</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45113</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45114</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45540</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45404</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>45660</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>46100</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45120</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>46107</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>46111</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45201</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>46112</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>46112</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>46112</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44904</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>46127</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45114</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44916</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45611</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45337</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>44894</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45204</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>46246</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>46246</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>44963</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>46246</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>46246</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45229</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>44533</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45114</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>46211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45303</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>44916</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45204</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45330</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45702</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46258</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>46083</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>46259</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45516</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46258</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>46261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45584</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>46260</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>46261</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>46261</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45488</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45175</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45153</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45048</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>46262</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>46262</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>46262</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>44643</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>45537</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45572</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>46262</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>44910</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>45709</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45709</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>44742</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45107</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>45034</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45348</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45310</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>46269</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>44496</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>46269</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>46268</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45783</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45783</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45539</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45785</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45432</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>46041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>46231</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>46274</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>46231</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45441</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45926</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>46276</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51971,7 +51971,7 @@
         <v>45121</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>45348</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>46233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>46233</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>46236</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>46233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45223</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45964</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45588</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>45453</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>46239</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45575</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45798</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45800</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>44865</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45804</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>45674</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45812</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45350</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45322</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45830</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45863</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>45415</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45874</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53929,7 +53929,7 @@
         <v>45875</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45114</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>44637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>44083</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45357</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44692</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>44692</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45355</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45356</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54621,7 +54621,7 @@
         <v>45684</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>44692</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>44715</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45356</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45359</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45359</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>44698</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45355</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>44602</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>45355</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45684</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55479,7 +55479,7 @@
         <v>44806</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55552,7 +55552,7 @@
         <v>45356</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55630,7 +55630,7 @@
         <v>45359</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>44602</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>45357</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>45357</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55942,7 +55942,7 @@
         <v>44602</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45356</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56098,7 +56098,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>44662</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56249,7 +56249,7 @@
         <v>45355</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>44708</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45684</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45715</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>45684</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45713</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45714</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45757</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>45757</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45757</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>45758</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45575</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57253,7 +57253,7 @@
         <v>45684</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>46089</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57409,7 +57409,7 @@
         <v>46089</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46104</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57643,7 +57643,7 @@
         <v>46104</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>46104</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>46104</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46105</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>46150</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>46048</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45173</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45901</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45700</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45524</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45502</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45110</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45833</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         <v>19</v>
       </c>
       <c r="T21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45278</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>46267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>46238</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45868</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>45118</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45919</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46259</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45988</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45945</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>44697</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>46057</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46108</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45407</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45929</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>46052</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>46058</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44543</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45393</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45159</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45912</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46267</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45909</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44846</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45415</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>46036</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46003</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>46057</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>46031</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45902</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45362</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44519</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44473</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37289-2026</t>
+          <t>A 33882-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>45522</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10885,26 +10885,21 @@
           <t>ÄLVDALEN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>11.1</v>
+        <v>53.8</v>
       </c>
       <c r="J83" t="n">
         <v>4</v>
       </c>
       <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5</v>
+      </c>
+      <c r="M83" t="n">
         <v>2</v>
       </c>
-      <c r="L83" t="n">
-        <v>3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
@@ -10915,21 +10910,143 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
       </c>
       <c r="T83" t="n">
+        <v>21</v>
+      </c>
+      <c r="U83" t="n">
+        <v>18</v>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggnål
+Knottrig blåslav
+Lavskrika
+Skrovellav
+Tretåig hackspett
+Vitplätt
+Spindelblomster
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 33882-2024 artfynd.xlsx", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="X83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 33882-2024 karta.png", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="Y83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 33882-2024 georefererad karta.tif", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="AA83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 33882-2024 FSC-klagomål.docx", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="AB83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 33882-2024 FSC-klagomål mail.docx", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="AC83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 33882-2024 tillsynsbegäran.docx", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="AD83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 33882-2024 tillsynsbegäran mail.docx", "A 33882-2024")</f>
+        <v/>
+      </c>
+      <c r="AE83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 33882-2024 prioriterade fågelarter.docx", "A 33882-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A 37289-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>4</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>9</v>
+      </c>
+      <c r="T84" t="n">
         <v>35</v>
       </c>
-      <c r="U83" t="n">
+      <c r="U84" t="n">
         <v>35</v>
       </c>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="V84" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Talltita
@@ -10942,116 +11059,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W83">
+      <c r="W84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 37289-2026 artfynd.xlsx", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="X83">
+      <c r="X84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 37289-2026 karta.png", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="Y83">
+      <c r="Y84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 37289-2026 georefererad karta.tif", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="AA83">
+      <c r="AA84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 37289-2026 FSC-klagomål.docx", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="AB83">
+      <c r="AB84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 37289-2026 FSC-klagomål mail.docx", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="AC83">
+      <c r="AC84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 37289-2026 tillsynsbegäran.docx", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="AD83">
+      <c r="AD84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 37289-2026 tillsynsbegäran mail.docx", "A 37289-2026")</f>
         <v/>
       </c>
-      <c r="AE83">
+      <c r="AE84">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 37289-2026 prioriterade fågelarter.docx", "A 37289-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>A 41913-2022</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D84" s="1" t="n">
+      <c r="D85" s="1" t="n">
         <v>44830</v>
       </c>
-      <c r="E84" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="E85" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I85" t="n">
         <v>5.6</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>7</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M85" t="n">
         <v>2</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
         <v>9</v>
       </c>
-      <c r="R84" t="n">
+      <c r="R85" t="n">
         <v>2</v>
       </c>
-      <c r="S84" t="n">
+      <c r="S85" t="n">
         <v>9</v>
       </c>
-      <c r="T84" t="n">
+      <c r="T85" t="n">
         <v>20</v>
       </c>
-      <c r="U84" t="n">
+      <c r="U85" t="n">
         <v>19</v>
       </c>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="V85" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Tajgataggsvamp
@@ -11064,116 +11181,116 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W84">
+      <c r="W85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 41913-2022 artfynd.xlsx", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="X84">
+      <c r="X85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 41913-2022 karta.png", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="Y84">
+      <c r="Y85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 41913-2022 georefererad karta.tif", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="AA84">
+      <c r="AA85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 41913-2022 FSC-klagomål.docx", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="AB84">
+      <c r="AB85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 41913-2022 FSC-klagomål mail.docx", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="AC84">
+      <c r="AC85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 41913-2022 tillsynsbegäran.docx", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="AD84">
+      <c r="AD85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 41913-2022 tillsynsbegäran mail.docx", "A 41913-2022")</f>
         <v/>
       </c>
-      <c r="AE84">
+      <c r="AE85">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 41913-2022 prioriterade fågelarter.docx", "A 41913-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>A 38741-2026</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D85" s="1" t="n">
+      <c r="D86" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="E85" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="E86" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I86" t="n">
         <v>10.1</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J86" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
         <v>7</v>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
         <v>1</v>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
         <v>8</v>
       </c>
-      <c r="R85" t="n">
+      <c r="R86" t="n">
         <v>1</v>
       </c>
-      <c r="S85" t="n">
+      <c r="S86" t="n">
         <v>9</v>
       </c>
-      <c r="T85" t="n">
+      <c r="T86" t="n">
         <v>10</v>
       </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2" t="inlineStr">
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
         <is>
           <t>Mosippa
 Dropptaggsvamp
@@ -11186,112 +11303,112 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W85">
+      <c r="W86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 38741-2026 artfynd.xlsx", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="X85">
+      <c r="X86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 38741-2026 karta.png", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="Y85">
+      <c r="Y86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 38741-2026 georefererad karta.tif", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="AA85">
+      <c r="AA86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 38741-2026 FSC-klagomål.docx", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="AB85">
+      <c r="AB86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 38741-2026 FSC-klagomål mail.docx", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="AC85">
+      <c r="AC86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 38741-2026 tillsynsbegäran.docx", "A 38741-2026")</f>
         <v/>
       </c>
-      <c r="AD85">
+      <c r="AD86">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 38741-2026 tillsynsbegäran mail.docx", "A 38741-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>A 20947-2026</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D86" s="1" t="n">
+      <c r="D87" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="E86" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="E87" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I87" t="n">
         <v>3.7</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J87" t="n">
         <v>7</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K87" t="n">
         <v>2</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L87" t="n">
         <v>1</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M87" t="n">
         <v>1</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
         <v>2</v>
       </c>
-      <c r="R86" t="n">
+      <c r="R87" t="n">
         <v>1</v>
       </c>
-      <c r="S86" t="n">
+      <c r="S87" t="n">
         <v>9</v>
       </c>
-      <c r="T86" t="n">
+      <c r="T87" t="n">
         <v>22</v>
       </c>
-      <c r="U86" t="n">
+      <c r="U87" t="n">
         <v>22</v>
       </c>
-      <c r="V86" s="2" t="inlineStr">
+      <c r="V87" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Järnsparv
@@ -11304,111 +11421,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W86">
+      <c r="W87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 20947-2026 artfynd.xlsx", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="X86">
+      <c r="X87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 20947-2026 karta.png", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="Y86">
+      <c r="Y87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 20947-2026 georefererad karta.tif", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="AA86">
+      <c r="AA87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 20947-2026 FSC-klagomål.docx", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="AB86">
+      <c r="AB87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 20947-2026 FSC-klagomål mail.docx", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="AC86">
+      <c r="AC87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 20947-2026 tillsynsbegäran.docx", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="AD86">
+      <c r="AD87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 20947-2026 tillsynsbegäran mail.docx", "A 20947-2026")</f>
         <v/>
       </c>
-      <c r="AE86">
+      <c r="AE87">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 20947-2026 prioriterade fågelarter.docx", "A 20947-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>A 39278-2022</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D87" s="1" t="n">
+      <c r="D88" s="1" t="n">
         <v>44817</v>
       </c>
-      <c r="E87" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
+      <c r="E88" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
         <v>20.3</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J88" t="n">
         <v>5</v>
       </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
         <v>6</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M88" t="n">
         <v>2</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
         <v>8</v>
       </c>
-      <c r="R87" t="n">
+      <c r="R88" t="n">
         <v>2</v>
       </c>
-      <c r="S87" t="n">
+      <c r="S88" t="n">
         <v>9</v>
       </c>
-      <c r="T87" t="n">
+      <c r="T88" t="n">
         <v>10</v>
       </c>
-      <c r="U87" t="n">
+      <c r="U88" t="n">
         <v>6</v>
       </c>
-      <c r="V87" s="2" t="inlineStr">
+      <c r="V88" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Sprickporing
@@ -11421,116 +11538,116 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W87">
+      <c r="W88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 39278-2022 artfynd.xlsx", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="X87">
+      <c r="X88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 39278-2022 karta.png", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="Y87">
+      <c r="Y88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 39278-2022 georefererad karta.tif", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="AA87">
+      <c r="AA88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 39278-2022 FSC-klagomål.docx", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="AB87">
+      <c r="AB88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 39278-2022 FSC-klagomål mail.docx", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="AC87">
+      <c r="AC88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 39278-2022 tillsynsbegäran.docx", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="AD87">
+      <c r="AD88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 39278-2022 tillsynsbegäran mail.docx", "A 39278-2022")</f>
         <v/>
       </c>
-      <c r="AE87">
+      <c r="AE88">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 39278-2022 prioriterade fågelarter.docx", "A 39278-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>A 57505-2024</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D89" s="1" t="n">
         <v>45630</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="E89" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I88" t="n">
+      <c r="I89" t="n">
         <v>2.3</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J89" t="n">
         <v>2</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K89" t="n">
         <v>2</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L89" t="n">
         <v>6</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M89" t="n">
         <v>1</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
         <v>7</v>
       </c>
-      <c r="R88" t="n">
+      <c r="R89" t="n">
         <v>1</v>
       </c>
-      <c r="S88" t="n">
+      <c r="S89" t="n">
         <v>9</v>
       </c>
-      <c r="T88" t="n">
+      <c r="T89" t="n">
         <v>19</v>
       </c>
-      <c r="U88" t="n">
+      <c r="U89" t="n">
         <v>18</v>
       </c>
-      <c r="V88" s="2" t="inlineStr">
+      <c r="V89" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knottrig blåslav
@@ -11543,111 +11660,111 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="W88">
+      <c r="W89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 57505-2024 artfynd.xlsx", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="X88">
+      <c r="X89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 57505-2024 karta.png", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="Y88">
+      <c r="Y89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 57505-2024 georefererad karta.tif", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="AA88">
+      <c r="AA89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 57505-2024 FSC-klagomål.docx", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="AB88">
+      <c r="AB89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 57505-2024 FSC-klagomål mail.docx", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="AC88">
+      <c r="AC89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 57505-2024 tillsynsbegäran.docx", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="AD88">
+      <c r="AD89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 57505-2024 tillsynsbegäran mail.docx", "A 57505-2024")</f>
         <v/>
       </c>
-      <c r="AE88">
+      <c r="AE89">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 57505-2024 prioriterade fågelarter.docx", "A 57505-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>A 62684-2025</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D89" s="1" t="n">
+      <c r="D90" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
+      <c r="E90" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
         <v>20.3</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J90" t="n">
         <v>4</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K90" t="n">
         <v>2</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L90" t="n">
         <v>2</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="R89" t="n">
+      <c r="R90" t="n">
         <v>1</v>
       </c>
-      <c r="S89" t="n">
+      <c r="S90" t="n">
         <v>8</v>
       </c>
-      <c r="T89" t="n">
+      <c r="T90" t="n">
         <v>77</v>
       </c>
-      <c r="U89" t="n">
+      <c r="U90" t="n">
         <v>75</v>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blå taggsvamp
@@ -11659,111 +11776,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W89">
+      <c r="W90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 62684-2025 artfynd.xlsx", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="X89">
+      <c r="X90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 62684-2025 karta.png", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="Y89">
+      <c r="Y90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 62684-2025 georefererad karta.tif", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="AA89">
+      <c r="AA90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 62684-2025 FSC-klagomål.docx", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="AB89">
+      <c r="AB90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 62684-2025 FSC-klagomål mail.docx", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="AC89">
+      <c r="AC90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 62684-2025 tillsynsbegäran.docx", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="AD89">
+      <c r="AD90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 62684-2025 tillsynsbegäran mail.docx", "A 62684-2025")</f>
         <v/>
       </c>
-      <c r="AE89">
+      <c r="AE90">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 62684-2025 prioriterade fågelarter.docx", "A 62684-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>A 62355-2022</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D90" s="1" t="n">
+      <c r="D91" s="1" t="n">
         <v>44923</v>
       </c>
-      <c r="E90" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
+      <c r="E91" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
         <v>4.3</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J91" t="n">
         <v>4</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K91" t="n">
         <v>1</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M91" t="n">
         <v>2</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>5</v>
       </c>
-      <c r="R90" t="n">
+      <c r="R91" t="n">
         <v>2</v>
       </c>
-      <c r="S90" t="n">
+      <c r="S91" t="n">
         <v>8</v>
       </c>
-      <c r="T90" t="n">
+      <c r="T91" t="n">
         <v>15</v>
       </c>
-      <c r="U90" t="n">
+      <c r="U91" t="n">
         <v>15</v>
       </c>
-      <c r="V90" s="2" t="inlineStr">
+      <c r="V91" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -11775,115 +11892,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W90">
+      <c r="W91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 62355-2022 artfynd.xlsx", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="X90">
+      <c r="X91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 62355-2022 karta.png", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="Y90">
+      <c r="Y91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 62355-2022 georefererad karta.tif", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="Z90">
+      <c r="Z91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/knärot/A 62355-2022 karta knärot.png", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="AA90">
+      <c r="AA91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 62355-2022 FSC-klagomål.docx", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="AB90">
+      <c r="AB91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 62355-2022 FSC-klagomål mail.docx", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="AC90">
+      <c r="AC91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 62355-2022 tillsynsbegäran.docx", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="AD90">
+      <c r="AD91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 62355-2022 tillsynsbegäran mail.docx", "A 62355-2022")</f>
         <v/>
       </c>
-      <c r="AE90">
+      <c r="AE91">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 62355-2022 prioriterade fågelarter.docx", "A 62355-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>A 41750-2025</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D91" s="1" t="n">
+      <c r="D92" s="1" t="n">
         <v>45902</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
+      <c r="E92" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
         <v>1.2</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>6</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M92" t="n">
         <v>2</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
         <v>8</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R92" t="n">
         <v>2</v>
       </c>
-      <c r="S91" t="n">
+      <c r="S92" t="n">
         <v>8</v>
       </c>
-      <c r="T91" t="n">
+      <c r="T92" t="n">
         <v>13</v>
       </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr">
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
         <is>
           <t>Gräddporing
 Skrovlig taggsvamp
@@ -11895,112 +12012,112 @@
 Vedflamlav</t>
         </is>
       </c>
-      <c r="W91">
+      <c r="W92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 41750-2025 artfynd.xlsx", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="X91">
+      <c r="X92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 41750-2025 karta.png", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="Y91">
+      <c r="Y92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 41750-2025 georefererad karta.tif", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="AA91">
+      <c r="AA92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 41750-2025 FSC-klagomål.docx", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="AB91">
+      <c r="AB92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 41750-2025 FSC-klagomål mail.docx", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="AC91">
+      <c r="AC92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 41750-2025 tillsynsbegäran.docx", "A 41750-2025")</f>
         <v/>
       </c>
-      <c r="AD91">
+      <c r="AD92">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 41750-2025 tillsynsbegäran mail.docx", "A 41750-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>A 25754-2025</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D92" s="1" t="n">
+      <c r="D93" s="1" t="n">
         <v>45804</v>
       </c>
-      <c r="E92" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
+      <c r="E93" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I92" t="n">
+      <c r="I93" t="n">
         <v>2.2</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J93" t="n">
         <v>4</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K93" t="n">
         <v>1</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L93" t="n">
         <v>3</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M93" t="n">
         <v>1</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
         <v>4</v>
       </c>
-      <c r="R92" t="n">
+      <c r="R93" t="n">
         <v>1</v>
       </c>
-      <c r="S92" t="n">
+      <c r="S93" t="n">
         <v>8</v>
       </c>
-      <c r="T92" t="n">
+      <c r="T93" t="n">
         <v>15</v>
       </c>
-      <c r="U92" t="n">
+      <c r="U93" t="n">
         <v>15</v>
       </c>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="V93" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Dropptaggsvamp
@@ -12012,111 +12129,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W92">
+      <c r="W93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 25754-2025 artfynd.xlsx", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="X92">
+      <c r="X93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 25754-2025 karta.png", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="Y92">
+      <c r="Y93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 25754-2025 georefererad karta.tif", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="AA92">
+      <c r="AA93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 25754-2025 FSC-klagomål.docx", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="AB92">
+      <c r="AB93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 25754-2025 FSC-klagomål mail.docx", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="AC92">
+      <c r="AC93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 25754-2025 tillsynsbegäran.docx", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="AD92">
+      <c r="AD93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 25754-2025 tillsynsbegäran mail.docx", "A 25754-2025")</f>
         <v/>
       </c>
-      <c r="AE92">
+      <c r="AE93">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 25754-2025 prioriterade fågelarter.docx", "A 25754-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>A 54840-2025</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n">
+      <c r="D94" s="1" t="n">
         <v>45966</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
+      <c r="E94" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
         <v>16.3</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J94" t="n">
         <v>3</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K94" t="n">
         <v>2</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L94" t="n">
         <v>2</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M94" t="n">
         <v>1</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
         <v>3</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R94" t="n">
         <v>1</v>
       </c>
-      <c r="S93" t="n">
+      <c r="S94" t="n">
         <v>8</v>
       </c>
-      <c r="T93" t="n">
+      <c r="T94" t="n">
         <v>61</v>
       </c>
-      <c r="U93" t="n">
+      <c r="U94" t="n">
         <v>61</v>
       </c>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="V94" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Kolflarnlav
@@ -12128,111 +12245,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W93">
+      <c r="W94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 54840-2025 artfynd.xlsx", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="X93">
+      <c r="X94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 54840-2025 karta.png", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="Y93">
+      <c r="Y94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 54840-2025 georefererad karta.tif", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="AA93">
+      <c r="AA94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 54840-2025 FSC-klagomål.docx", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="AB93">
+      <c r="AB94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 54840-2025 FSC-klagomål mail.docx", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="AC93">
+      <c r="AC94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 54840-2025 tillsynsbegäran.docx", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="AD93">
+      <c r="AD94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 54840-2025 tillsynsbegäran mail.docx", "A 54840-2025")</f>
         <v/>
       </c>
-      <c r="AE93">
+      <c r="AE94">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 54840-2025 prioriterade fågelarter.docx", "A 54840-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>A 66887-2021</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D94" s="1" t="n">
+      <c r="D95" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E94" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
+      <c r="E95" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
         <v>1.8</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>7</v>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M95" t="n">
         <v>1</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
         <v>2</v>
       </c>
-      <c r="R94" t="n">
+      <c r="R95" t="n">
         <v>1</v>
       </c>
-      <c r="S94" t="n">
+      <c r="S95" t="n">
         <v>8</v>
       </c>
-      <c r="T94" t="n">
+      <c r="T95" t="n">
         <v>10</v>
       </c>
-      <c r="U94" t="n">
+      <c r="U95" t="n">
         <v>10</v>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="V95" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Järnsparv
@@ -12244,115 +12361,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W94">
+      <c r="W95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 66887-2021 artfynd.xlsx", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="X94">
+      <c r="X95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 66887-2021 karta.png", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="Y94">
+      <c r="Y95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 66887-2021 georefererad karta.tif", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="Z94">
+      <c r="Z95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/knärot/A 66887-2021 karta knärot.png", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="AA94">
+      <c r="AA95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 66887-2021 FSC-klagomål.docx", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="AB94">
+      <c r="AB95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 66887-2021 FSC-klagomål mail.docx", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="AC94">
+      <c r="AC95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 66887-2021 tillsynsbegäran.docx", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="AD94">
+      <c r="AD95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 66887-2021 tillsynsbegäran mail.docx", "A 66887-2021")</f>
         <v/>
       </c>
-      <c r="AE94">
+      <c r="AE95">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 66887-2021 prioriterade fågelarter.docx", "A 66887-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>A 24018-2026</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D95" s="1" t="n">
+      <c r="D96" s="1" t="n">
         <v>46167</v>
       </c>
-      <c r="E95" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
+      <c r="E96" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
         <v>1.1</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>7</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M96" t="n">
         <v>1</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>2</v>
       </c>
-      <c r="R95" t="n">
+      <c r="R96" t="n">
         <v>1</v>
       </c>
-      <c r="S95" t="n">
+      <c r="S96" t="n">
         <v>8</v>
       </c>
-      <c r="T95" t="n">
+      <c r="T96" t="n">
         <v>10</v>
       </c>
-      <c r="U95" t="n">
+      <c r="U96" t="n">
         <v>10</v>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Järnsparv
@@ -12364,120 +12481,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W95">
+      <c r="W96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 24018-2026 artfynd.xlsx", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="X95">
+      <c r="X96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 24018-2026 karta.png", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="Y95">
+      <c r="Y96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 24018-2026 georefererad karta.tif", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="Z95">
+      <c r="Z96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/knärot/A 24018-2026 karta knärot.png", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="AA95">
+      <c r="AA96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 24018-2026 FSC-klagomål.docx", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="AB95">
+      <c r="AB96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 24018-2026 FSC-klagomål mail.docx", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="AC95">
+      <c r="AC96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 24018-2026 tillsynsbegäran.docx", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="AD95">
+      <c r="AD96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 24018-2026 tillsynsbegäran mail.docx", "A 24018-2026")</f>
         <v/>
       </c>
-      <c r="AE95">
+      <c r="AE96">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 24018-2026 prioriterade fågelarter.docx", "A 24018-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>A 50385-2024</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D96" s="1" t="n">
+      <c r="D97" s="1" t="n">
         <v>45600</v>
       </c>
-      <c r="E96" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
+      <c r="E97" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I96" t="n">
+      <c r="I97" t="n">
         <v>13.9</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>2</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L97" t="n">
         <v>5</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M97" t="n">
         <v>1</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
         <v>6</v>
       </c>
-      <c r="R96" t="n">
+      <c r="R97" t="n">
         <v>1</v>
       </c>
-      <c r="S96" t="n">
+      <c r="S97" t="n">
         <v>8</v>
       </c>
-      <c r="T96" t="n">
+      <c r="T97" t="n">
         <v>9</v>
       </c>
-      <c r="U96" t="n">
+      <c r="U97" t="n">
         <v>9</v>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Duvhök
@@ -12489,111 +12606,111 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="W96">
+      <c r="W97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 50385-2024 artfynd.xlsx", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="X96">
+      <c r="X97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 50385-2024 karta.png", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="Y96">
+      <c r="Y97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 50385-2024 georefererad karta.tif", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="AA96">
+      <c r="AA97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 50385-2024 FSC-klagomål.docx", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="AB96">
+      <c r="AB97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 50385-2024 FSC-klagomål mail.docx", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="AC96">
+      <c r="AC97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 50385-2024 tillsynsbegäran.docx", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="AD96">
+      <c r="AD97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 50385-2024 tillsynsbegäran mail.docx", "A 50385-2024")</f>
         <v/>
       </c>
-      <c r="AE96">
+      <c r="AE97">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 50385-2024 prioriterade fågelarter.docx", "A 50385-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>A 11125-2026</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D97" s="1" t="n">
+      <c r="D98" s="1" t="n">
         <v>46079</v>
       </c>
-      <c r="E97" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
+      <c r="E98" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
         <v>10.5</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J98" t="n">
         <v>2</v>
       </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>6</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M98" t="n">
         <v>2</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
         <v>8</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R98" t="n">
         <v>2</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S98" t="n">
         <v>8</v>
       </c>
-      <c r="T97" t="n">
+      <c r="T98" t="n">
         <v>20</v>
       </c>
-      <c r="U97" t="n">
+      <c r="U98" t="n">
         <v>20</v>
       </c>
-      <c r="V97" s="2" t="inlineStr">
+      <c r="V98" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gräddporing
@@ -12605,152 +12722,36 @@
 Violettgrå tagellav</t>
         </is>
       </c>
-      <c r="W97">
+      <c r="W98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 11125-2026 artfynd.xlsx", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="X97">
+      <c r="X98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 11125-2026 karta.png", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="Y97">
+      <c r="Y98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 11125-2026 georefererad karta.tif", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="AA97">
+      <c r="AA98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 11125-2026 FSC-klagomål.docx", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="AB97">
+      <c r="AB98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 11125-2026 FSC-klagomål mail.docx", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="AC97">
+      <c r="AC98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 11125-2026 tillsynsbegäran.docx", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="AD97">
+      <c r="AD98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 11125-2026 tillsynsbegäran mail.docx", "A 11125-2026")</f>
         <v/>
       </c>
-      <c r="AE97">
+      <c r="AE98">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 11125-2026 prioriterade fågelarter.docx", "A 11125-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>A 33882-2024</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D98" s="1" t="n">
-        <v>45522</v>
-      </c>
-      <c r="E98" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" t="n">
-        <v>4</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>6</v>
-      </c>
-      <c r="R98" t="n">
-        <v>2</v>
-      </c>
-      <c r="S98" t="n">
-        <v>8</v>
-      </c>
-      <c r="T98" t="n">
-        <v>18</v>
-      </c>
-      <c r="U98" t="n">
-        <v>15</v>
-      </c>
-      <c r="V98" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggnål
-Lavskrika
-Skrovellav
-Tretåig hackspett
-Vitplätt
-Spindelblomster
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 33882-2024 artfynd.xlsx", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="X98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 33882-2024 karta.png", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="Y98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 33882-2024 georefererad karta.tif", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="AA98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 33882-2024 FSC-klagomål.docx", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="AB98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 33882-2024 FSC-klagomål mail.docx", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="AC98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 33882-2024 tillsynsbegäran.docx", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="AD98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 33882-2024 tillsynsbegäran mail.docx", "A 33882-2024")</f>
-        <v/>
-      </c>
-      <c r="AE98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 33882-2024 prioriterade fågelarter.docx", "A 33882-2024")</f>
         <v/>
       </c>
     </row>
@@ -12774,7 +12775,7 @@
         <v>46238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12895,7 +12896,7 @@
         <v>45988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13016,7 +13017,7 @@
         <v>45943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13137,7 +13138,7 @@
         <v>45593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13257,7 +13258,7 @@
         <v>45210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13373,7 +13374,7 @@
         <v>46057</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13488,7 +13489,7 @@
         <v>45968</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13604,7 +13605,7 @@
         <v>45987</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13720,7 +13721,7 @@
         <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13840,7 +13841,7 @@
         <v>45834</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13956,7 +13957,7 @@
         <v>45162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14072,7 +14073,7 @@
         <v>45895</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14187,7 +14188,7 @@
         <v>46272</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14303,7 +14304,7 @@
         <v>46238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14423,7 +14424,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14543,7 +14544,7 @@
         <v>44828</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14654,7 +14655,7 @@
         <v>44971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14774,7 +14775,7 @@
         <v>44472</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14884,7 +14885,7 @@
         <v>45365</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15002,7 +15003,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15121,7 +15122,7 @@
         <v>45448</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15236,7 +15237,7 @@
         <v>46134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15350,7 +15351,7 @@
         <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15465,7 +15466,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15580,7 +15581,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15695,7 +15696,7 @@
         <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15810,7 +15811,7 @@
         <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15924,7 +15925,7 @@
         <v>45799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16038,7 +16039,7 @@
         <v>45902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16156,7 +16157,7 @@
         <v>45755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16270,7 +16271,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16388,7 +16389,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16501,7 +16502,7 @@
         <v>45173</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16619,7 +16620,7 @@
         <v>46283</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16737,7 +16738,7 @@
         <v>46287</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16851,7 +16852,7 @@
         <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16965,7 +16966,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17079,7 +17080,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17193,7 +17194,7 @@
         <v>46287</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17307,7 +17308,7 @@
         <v>44830</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17424,7 +17425,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17537,7 +17538,7 @@
         <v>45800</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17650,7 +17651,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17763,7 +17764,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17876,7 +17877,7 @@
         <v>45511</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17989,7 +17990,7 @@
         <v>45638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18102,7 +18103,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18215,7 +18216,7 @@
         <v>46057</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18327,7 +18328,7 @@
         <v>46189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18440,7 +18441,7 @@
         <v>45511</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18553,7 +18554,7 @@
         <v>46202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18665,7 +18666,7 @@
         <v>46254</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18778,7 +18779,7 @@
         <v>46212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18886,7 +18887,7 @@
         <v>46212</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18994,7 +18995,7 @@
         <v>45547</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19107,7 +19108,7 @@
         <v>46236</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19224,7 +19225,7 @@
         <v>45182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19337,7 +19338,7 @@
         <v>45786</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19450,7 +19451,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19562,7 +19563,7 @@
         <v>45343</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19674,7 +19675,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19786,7 +19787,7 @@
         <v>46127</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19893,7 +19894,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20009,7 +20010,7 @@
         <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20121,7 +20122,7 @@
         <v>45817</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20233,7 +20234,7 @@
         <v>45841</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20345,7 +20346,7 @@
         <v>46195</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20457,7 +20458,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20573,7 +20574,7 @@
         <v>45502</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20685,7 +20686,7 @@
         <v>45426</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20797,7 +20798,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20909,7 +20910,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21020,7 +21021,7 @@
         <v>44874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21126,7 +21127,7 @@
         <v>46121</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21241,7 +21242,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21352,7 +21353,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21463,7 +21464,7 @@
         <v>45817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21574,7 +21575,7 @@
         <v>44473</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21680,7 +21681,7 @@
         <v>45833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21795,7 +21796,7 @@
         <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21906,7 +21907,7 @@
         <v>45895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22016,7 +22017,7 @@
         <v>46196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22127,7 +22128,7 @@
         <v>44706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22238,7 +22239,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22349,7 +22350,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22459,7 +22460,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22570,7 +22571,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22680,7 +22681,7 @@
         <v>45496</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22786,7 +22787,7 @@
         <v>45404</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22892,7 +22893,7 @@
         <v>45902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23003,7 +23004,7 @@
         <v>46106</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23118,7 +23119,7 @@
         <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23229,7 +23230,7 @@
         <v>44516</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23339,7 +23340,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23449,7 +23450,7 @@
         <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23559,7 +23560,7 @@
         <v>44881</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23669,7 +23670,7 @@
         <v>45502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23778,7 +23779,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23888,7 +23889,7 @@
         <v>46058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23997,7 +23998,7 @@
         <v>45511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24107,7 +24108,7 @@
         <v>45938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24217,7 +24218,7 @@
         <v>46127</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24327,7 +24328,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24437,7 +24438,7 @@
         <v>45989</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24547,7 +24548,7 @@
         <v>45993</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24652,7 +24653,7 @@
         <v>45153</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24761,7 +24762,7 @@
         <v>46002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24871,7 +24872,7 @@
         <v>44873</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24981,7 +24982,7 @@
         <v>45853</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25091,7 +25092,7 @@
         <v>45770</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25201,7 +25202,7 @@
         <v>46177</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25311,7 +25312,7 @@
         <v>46189</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25421,7 +25422,7 @@
         <v>45572</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25535,7 +25536,7 @@
         <v>45792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25640,7 +25641,7 @@
         <v>45432</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25750,7 +25751,7 @@
         <v>45181</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25855,7 +25856,7 @@
         <v>46261</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25960,7 +25961,7 @@
         <v>46266</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26074,7 +26075,7 @@
         <v>46223</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26183,7 +26184,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26293,7 +26294,7 @@
         <v>46233</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26398,7 +26399,7 @@
         <v>46248</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26508,7 +26509,7 @@
         <v>46246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26613,7 +26614,7 @@
         <v>45786</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26723,7 +26724,7 @@
         <v>44629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26837,7 +26838,7 @@
         <v>44575</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26951,7 +26952,7 @@
         <v>45684</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27061,7 +27062,7 @@
         <v>45903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27171,7 +27172,7 @@
         <v>44662</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27244,7 +27245,7 @@
         <v>44754</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27317,7 +27318,7 @@
         <v>44810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27395,7 +27396,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27468,7 +27469,7 @@
         <v>44471</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27541,7 +27542,7 @@
         <v>44651</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27614,7 +27615,7 @@
         <v>44755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27687,7 +27688,7 @@
         <v>44519</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27765,7 +27766,7 @@
         <v>44477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27843,7 +27844,7 @@
         <v>44552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27921,7 +27922,7 @@
         <v>44817</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27999,7 +28000,7 @@
         <v>44873</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28072,7 +28073,7 @@
         <v>44504</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28150,7 +28151,7 @@
         <v>44846</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28223,7 +28224,7 @@
         <v>44467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28301,7 +28302,7 @@
         <v>44538</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28379,7 +28380,7 @@
         <v>44865</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28457,7 +28458,7 @@
         <v>44697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28530,7 +28531,7 @@
         <v>44477</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28608,7 +28609,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28681,7 +28682,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28754,7 +28755,7 @@
         <v>44484</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28827,7 +28828,7 @@
         <v>44477</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28900,7 +28901,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28978,7 +28979,7 @@
         <v>44539</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29051,7 +29052,7 @@
         <v>44536</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29129,7 +29130,7 @@
         <v>44680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29207,7 +29208,7 @@
         <v>44607</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29280,7 +29281,7 @@
         <v>44882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29358,7 +29359,7 @@
         <v>44636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29431,7 +29432,7 @@
         <v>44816</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29509,7 +29510,7 @@
         <v>44547</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29587,7 +29588,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29665,7 +29666,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29738,7 +29739,7 @@
         <v>44844</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29816,7 +29817,7 @@
         <v>45310</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29889,7 +29890,7 @@
         <v>45210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29962,7 +29963,7 @@
         <v>45229</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30035,7 +30036,7 @@
         <v>45420</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30113,7 +30114,7 @@
         <v>45477</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30186,7 +30187,7 @@
         <v>45477</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30259,7 +30260,7 @@
         <v>45114</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30332,7 +30333,7 @@
         <v>45545</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30405,7 +30406,7 @@
         <v>45512</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30483,7 +30484,7 @@
         <v>45702</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30561,7 +30562,7 @@
         <v>46014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30634,7 +30635,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30712,7 +30713,7 @@
         <v>44844</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30785,7 +30786,7 @@
         <v>44476</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30858,7 +30859,7 @@
         <v>44894</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30931,7 +30932,7 @@
         <v>45453</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31004,7 +31005,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31077,7 +31078,7 @@
         <v>45588</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31150,7 +31151,7 @@
         <v>46029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31223,7 +31224,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31296,7 +31297,7 @@
         <v>45330</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31369,7 +31370,7 @@
         <v>46029</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31442,7 +31443,7 @@
         <v>46029</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31515,7 +31516,7 @@
         <v>45488</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31588,7 +31589,7 @@
         <v>45488</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31661,7 +31662,7 @@
         <v>46035</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31739,7 +31740,7 @@
         <v>45887</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31817,7 +31818,7 @@
         <v>45357</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31895,7 +31896,7 @@
         <v>46038</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31968,7 +31969,7 @@
         <v>46038</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32041,7 +32042,7 @@
         <v>46038</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32114,7 +32115,7 @@
         <v>46038</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32187,7 +32188,7 @@
         <v>45548</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32260,7 +32261,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32333,7 +32334,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32406,7 +32407,7 @@
         <v>46038</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32479,7 +32480,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32557,7 +32558,7 @@
         <v>46038</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32630,7 +32631,7 @@
         <v>46041</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32703,7 +32704,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32776,7 +32777,7 @@
         <v>46042</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32849,7 +32850,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32927,7 +32928,7 @@
         <v>44873</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33000,7 +33001,7 @@
         <v>46043</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33073,7 +33074,7 @@
         <v>46044</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33146,7 +33147,7 @@
         <v>46043</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33219,7 +33220,7 @@
         <v>46043</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33292,7 +33293,7 @@
         <v>44526</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33370,7 +33371,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33443,7 +33444,7 @@
         <v>45898</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33516,7 +33517,7 @@
         <v>45770</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33594,7 +33595,7 @@
         <v>45646</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33667,7 +33668,7 @@
         <v>45665</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33740,7 +33741,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33813,7 +33814,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33891,7 +33892,7 @@
         <v>45911</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33964,7 +33965,7 @@
         <v>46057</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34037,7 +34038,7 @@
         <v>46062</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34110,7 +34111,7 @@
         <v>46062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34183,7 +34184,7 @@
         <v>46062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34256,7 +34257,7 @@
         <v>46062</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34329,7 +34330,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34407,7 +34408,7 @@
         <v>46062</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34480,7 +34481,7 @@
         <v>44874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34553,7 +34554,7 @@
         <v>45491</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34626,7 +34627,7 @@
         <v>45516</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34699,7 +34700,7 @@
         <v>45919</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34777,7 +34778,7 @@
         <v>46066</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34850,7 +34851,7 @@
         <v>44865</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34928,7 +34929,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35001,7 +35002,7 @@
         <v>46071</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35074,7 +35075,7 @@
         <v>45572</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35152,7 +35153,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35230,7 +35231,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35303,7 +35304,7 @@
         <v>46073</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35376,7 +35377,7 @@
         <v>45212</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35454,7 +35455,7 @@
         <v>45572</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35532,7 +35533,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35610,7 +35611,7 @@
         <v>45335</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35683,7 +35684,7 @@
         <v>45929</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35761,7 +35762,7 @@
         <v>46078</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35834,7 +35835,7 @@
         <v>45931</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35907,7 +35908,7 @@
         <v>45709</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35980,7 +35981,7 @@
         <v>45674</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36053,7 +36054,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36126,7 +36127,7 @@
         <v>46085</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36199,7 +36200,7 @@
         <v>45933</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36272,7 +36273,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36345,7 +36346,7 @@
         <v>45233</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36423,7 +36424,7 @@
         <v>46100</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36496,7 +36497,7 @@
         <v>45812</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36574,7 +36575,7 @@
         <v>45950</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36647,7 +36648,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36720,7 +36721,7 @@
         <v>45950</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36798,7 +36799,7 @@
         <v>45950</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36876,7 +36877,7 @@
         <v>45952</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36954,7 +36955,7 @@
         <v>45952</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37032,7 +37033,7 @@
         <v>45952</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37110,7 +37111,7 @@
         <v>46107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37188,7 +37189,7 @@
         <v>45952</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37266,7 +37267,7 @@
         <v>45953</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37344,7 +37345,7 @@
         <v>45348</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37417,7 +37418,7 @@
         <v>46112</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37490,7 +37491,7 @@
         <v>46112</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37563,7 +37564,7 @@
         <v>44916</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37636,7 +37637,7 @@
         <v>45307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37709,7 +37710,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37787,7 +37788,7 @@
         <v>46127</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37860,7 +37861,7 @@
         <v>45968</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37938,7 +37939,7 @@
         <v>45973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38016,7 +38017,7 @@
         <v>45973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38094,7 +38095,7 @@
         <v>46127</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38167,7 +38168,7 @@
         <v>45350</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38245,7 +38246,7 @@
         <v>45974</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38318,7 +38319,7 @@
         <v>45638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38396,7 +38397,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38469,7 +38470,7 @@
         <v>45114</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38547,7 +38548,7 @@
         <v>45986</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38625,7 +38626,7 @@
         <v>45988</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38698,7 +38699,7 @@
         <v>44755</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38771,7 +38772,7 @@
         <v>45988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38844,7 +38845,7 @@
         <v>45988</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38917,7 +38918,7 @@
         <v>45660</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38995,7 +38996,7 @@
         <v>45722</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39073,7 +39074,7 @@
         <v>45722</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39151,7 +39152,7 @@
         <v>45992</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39229,7 +39230,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39307,7 +39308,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39385,7 +39386,7 @@
         <v>45322</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39458,7 +39459,7 @@
         <v>45994</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39536,7 +39537,7 @@
         <v>45201</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39614,7 +39615,7 @@
         <v>45076</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39687,7 +39688,7 @@
         <v>45996</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39760,7 +39761,7 @@
         <v>44978</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39833,7 +39834,7 @@
         <v>45901</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39906,7 +39907,7 @@
         <v>44820</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39979,7 +39980,7 @@
         <v>44859</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40057,7 +40058,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40130,7 +40131,7 @@
         <v>45709</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40208,7 +40209,7 @@
         <v>46006</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40281,7 +40282,7 @@
         <v>44473</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40378,7 +40379,7 @@
         <v>46003</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40451,7 +40452,7 @@
         <v>45679</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40524,7 +40525,7 @@
         <v>46009</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40597,7 +40598,7 @@
         <v>45048</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40670,7 +40671,7 @@
         <v>46013</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40743,7 +40744,7 @@
         <v>45337</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40816,7 +40817,7 @@
         <v>45630</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40889,7 +40890,7 @@
         <v>45110</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40967,7 +40968,7 @@
         <v>46037</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41040,7 +41041,7 @@
         <v>46079</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41113,7 +41114,7 @@
         <v>44533</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41186,7 +41187,7 @@
         <v>45107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41259,7 +41260,7 @@
         <v>45589</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41332,7 +41333,7 @@
         <v>45709</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41405,7 +41406,7 @@
         <v>46043</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41478,7 +41479,7 @@
         <v>46148</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41551,7 +41552,7 @@
         <v>46148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41624,7 +41625,7 @@
         <v>46148</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41697,7 +41698,7 @@
         <v>44911</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41770,7 +41771,7 @@
         <v>45830</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41843,7 +41844,7 @@
         <v>46149</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41921,7 +41922,7 @@
         <v>46149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41999,7 +42000,7 @@
         <v>46149</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42077,7 +42078,7 @@
         <v>45175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42150,7 +42151,7 @@
         <v>44754</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42223,7 +42224,7 @@
         <v>45253</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42296,7 +42297,7 @@
         <v>46154</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42369,7 +42370,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42442,7 +42443,7 @@
         <v>45113</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42520,7 +42521,7 @@
         <v>45015</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42593,7 +42594,7 @@
         <v>44495</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42671,7 +42672,7 @@
         <v>44963</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42744,7 +42745,7 @@
         <v>45848</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42817,7 +42818,7 @@
         <v>45848</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42890,7 +42891,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42968,7 +42969,7 @@
         <v>45113</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43046,7 +43047,7 @@
         <v>45310</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43119,7 +43120,7 @@
         <v>45310</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43192,7 +43193,7 @@
         <v>45863</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43270,7 +43271,7 @@
         <v>45925</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43343,7 +43344,7 @@
         <v>45335</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43416,7 +43417,7 @@
         <v>44505</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43494,7 +43495,7 @@
         <v>46174</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43567,7 +43568,7 @@
         <v>44558</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43640,7 +43641,7 @@
         <v>46052</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43713,7 +43714,7 @@
         <v>46174</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43786,7 +43787,7 @@
         <v>46174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43859,7 +43860,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43932,7 +43933,7 @@
         <v>46030</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44005,7 +44006,7 @@
         <v>45415</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44078,7 +44079,7 @@
         <v>46177</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44151,7 +44152,7 @@
         <v>45141</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44224,7 +44225,7 @@
         <v>45034</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44297,7 +44298,7 @@
         <v>45874</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44375,7 +44376,7 @@
         <v>45201</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44453,7 +44454,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44526,7 +44527,7 @@
         <v>45588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44599,7 +44600,7 @@
         <v>45120</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44672,7 +44673,7 @@
         <v>45875</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44745,7 +44746,7 @@
         <v>45204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44818,7 +44819,7 @@
         <v>45114</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44891,7 +44892,7 @@
         <v>44568</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44964,7 +44965,7 @@
         <v>45638</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45042,7 +45043,7 @@
         <v>45665</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45115,7 +45116,7 @@
         <v>45665</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45188,7 +45189,7 @@
         <v>44558</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45261,7 +45262,7 @@
         <v>45491</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45334,7 +45335,7 @@
         <v>45114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45407,7 +45408,7 @@
         <v>44643</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45485,7 +45486,7 @@
         <v>45456</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45558,7 +45559,7 @@
         <v>45456</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45631,7 +45632,7 @@
         <v>46252</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45704,7 +45705,7 @@
         <v>45404</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45777,7 +45778,7 @@
         <v>45240</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45855,7 +45856,7 @@
         <v>45240</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45933,7 +45934,7 @@
         <v>46211</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46006,7 +46007,7 @@
         <v>46258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46079,7 +46080,7 @@
         <v>46258</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46152,7 +46153,7 @@
         <v>45210</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46230,7 +46231,7 @@
         <v>45700</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46308,7 +46309,7 @@
         <v>46258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46381,7 +46382,7 @@
         <v>46258</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46454,7 +46455,7 @@
         <v>45693</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46527,7 +46528,7 @@
         <v>46259</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46605,7 +46606,7 @@
         <v>45456</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46678,7 +46679,7 @@
         <v>46083</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46751,7 +46752,7 @@
         <v>45153</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46824,7 +46825,7 @@
         <v>46260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46897,7 +46898,7 @@
         <v>46262</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46970,7 +46971,7 @@
         <v>46261</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47043,7 +47044,7 @@
         <v>46261</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47116,7 +47117,7 @@
         <v>45114</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47189,7 +47190,7 @@
         <v>46262</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47262,7 +47263,7 @@
         <v>46262</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47335,7 +47336,7 @@
         <v>46262</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47408,7 +47409,7 @@
         <v>46261</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47486,7 +47487,7 @@
         <v>45322</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47559,7 +47560,7 @@
         <v>45159</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47637,7 +47638,7 @@
         <v>45303</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47710,7 +47711,7 @@
         <v>45537</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47783,7 +47784,7 @@
         <v>45336</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47856,7 +47857,7 @@
         <v>46268</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47929,7 +47930,7 @@
         <v>44839</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48002,7 +48003,7 @@
         <v>44526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48080,7 +48081,7 @@
         <v>45484</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48153,7 +48154,7 @@
         <v>46269</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48226,7 +48227,7 @@
         <v>46269</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48299,7 +48300,7 @@
         <v>45322</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48372,7 +48373,7 @@
         <v>45310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48445,7 +48446,7 @@
         <v>46041</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48518,7 +48519,7 @@
         <v>46231</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48596,7 +48597,7 @@
         <v>46231</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48674,7 +48675,7 @@
         <v>45204</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48747,7 +48748,7 @@
         <v>45507</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48820,7 +48821,7 @@
         <v>46276</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48898,7 +48899,7 @@
         <v>46233</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48976,7 +48977,7 @@
         <v>45077</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49049,7 +49050,7 @@
         <v>45550</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49122,7 +49123,7 @@
         <v>46236</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49200,7 +49201,7 @@
         <v>46233</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49278,7 +49279,7 @@
         <v>45299</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49351,7 +49352,7 @@
         <v>45964</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49424,7 +49425,7 @@
         <v>45328</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49497,7 +49498,7 @@
         <v>46233</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49575,7 +49576,7 @@
         <v>45691</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49653,7 +49654,7 @@
         <v>45540</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49726,7 +49727,7 @@
         <v>46239</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49804,7 +49805,7 @@
         <v>45566</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49882,7 +49883,7 @@
         <v>46286</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49960,7 +49961,7 @@
         <v>45327</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50033,7 +50034,7 @@
         <v>45560</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50111,7 +50112,7 @@
         <v>44678</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50184,7 +50185,7 @@
         <v>44910</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50257,7 +50258,7 @@
         <v>44904</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50330,7 +50331,7 @@
         <v>46112</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50403,7 +50404,7 @@
         <v>45247</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50476,7 +50477,7 @@
         <v>46246</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50549,7 +50550,7 @@
         <v>46288</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50622,7 +50623,7 @@
         <v>46288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50695,7 +50696,7 @@
         <v>45246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50768,7 +50769,7 @@
         <v>45072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50846,7 +50847,7 @@
         <v>45175</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50919,7 +50920,7 @@
         <v>46246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50992,7 +50993,7 @@
         <v>44755</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51070,7 +51071,7 @@
         <v>44496</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51148,7 +51149,7 @@
         <v>46246</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51221,7 +51222,7 @@
         <v>45926</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51327,7 +51328,7 @@
         <v>45597</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51400,7 +51401,7 @@
         <v>45356</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51473,7 +51474,7 @@
         <v>45575</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51546,7 +51547,7 @@
         <v>46246</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51619,7 +51620,7 @@
         <v>45106</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51692,7 +51693,7 @@
         <v>44888</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51765,7 +51766,7 @@
         <v>45485</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51838,7 +51839,7 @@
         <v>44873</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51911,7 +51912,7 @@
         <v>45254</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51984,7 +51985,7 @@
         <v>45477</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52057,7 +52058,7 @@
         <v>45584</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52130,7 +52131,7 @@
         <v>44896</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52208,7 +52209,7 @@
         <v>45584</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52281,7 +52282,7 @@
         <v>44651</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52359,7 +52360,7 @@
         <v>45274</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52432,7 +52433,7 @@
         <v>45322</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52505,7 +52506,7 @@
         <v>45322</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52578,7 +52579,7 @@
         <v>45700</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52651,7 +52652,7 @@
         <v>45307</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52724,7 +52725,7 @@
         <v>45247</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52797,7 +52798,7 @@
         <v>45104</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52875,7 +52876,7 @@
         <v>45124</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52948,7 +52949,7 @@
         <v>45299</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53021,7 +53022,7 @@
         <v>45209</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53094,7 +53095,7 @@
         <v>45534</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53167,7 +53168,7 @@
         <v>45204</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53240,7 +53241,7 @@
         <v>45253</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53313,7 +53314,7 @@
         <v>45246</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53386,7 +53387,7 @@
         <v>45611</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53459,7 +53460,7 @@
         <v>45783</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53532,7 +53533,7 @@
         <v>45783</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53605,7 +53606,7 @@
         <v>45539</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53678,7 +53679,7 @@
         <v>45348</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53751,7 +53752,7 @@
         <v>45121</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53824,7 +53825,7 @@
         <v>45785</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53902,7 +53903,7 @@
         <v>45432</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53975,7 +53976,7 @@
         <v>45441</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54048,7 +54049,7 @@
         <v>45223</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54121,7 +54122,7 @@
         <v>44083</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54199,7 +54200,7 @@
         <v>44637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54277,7 +54278,7 @@
         <v>44692</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54355,7 +54356,7 @@
         <v>44692</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54433,7 +54434,7 @@
         <v>44692</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54511,7 +54512,7 @@
         <v>44715</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54589,7 +54590,7 @@
         <v>44698</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54667,7 +54668,7 @@
         <v>44602</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54745,7 +54746,7 @@
         <v>44602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54823,7 +54824,7 @@
         <v>44602</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54901,7 +54902,7 @@
         <v>44662</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54974,7 +54975,7 @@
         <v>44708</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55052,7 +55053,7 @@
         <v>45357</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55130,7 +55131,7 @@
         <v>45355</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55208,7 +55209,7 @@
         <v>45356</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55286,7 +55287,7 @@
         <v>45684</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55364,7 +55365,7 @@
         <v>45356</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55442,7 +55443,7 @@
         <v>45359</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55520,7 +55521,7 @@
         <v>45359</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55598,7 +55599,7 @@
         <v>45355</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55676,7 +55677,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55754,7 +55755,7 @@
         <v>45684</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55832,7 +55833,7 @@
         <v>44806</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55905,7 +55906,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55983,7 +55984,7 @@
         <v>45359</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56061,7 +56062,7 @@
         <v>45357</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56139,7 +56140,7 @@
         <v>45357</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56217,7 +56218,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56295,7 +56296,7 @@
         <v>45356</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56373,7 +56374,7 @@
         <v>45355</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56451,7 +56452,7 @@
         <v>45684</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56529,7 +56530,7 @@
         <v>45715</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56602,7 +56603,7 @@
         <v>45684</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56680,7 +56681,7 @@
         <v>45713</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56758,7 +56759,7 @@
         <v>45714</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56836,7 +56837,7 @@
         <v>45758</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56914,7 +56915,7 @@
         <v>45757</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56992,7 +56993,7 @@
         <v>45757</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57070,7 +57071,7 @@
         <v>45757</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57148,7 +57149,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57226,7 +57227,7 @@
         <v>45575</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57299,7 +57300,7 @@
         <v>45684</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57377,7 +57378,7 @@
         <v>46089</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57455,7 +57456,7 @@
         <v>46089</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57533,7 +57534,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57611,7 +57612,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57689,7 +57690,7 @@
         <v>46105</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57767,7 +57768,7 @@
         <v>46104</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57845,7 +57846,7 @@
         <v>46104</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57923,7 +57924,7 @@
         <v>46104</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -58001,7 +58002,7 @@
         <v>46150</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>46048</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45173</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45901</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45700</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45524</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45502</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45110</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45833</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45278</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>46267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>46238</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45868</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>45118</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45919</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>46259</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45988</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45945</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>44697</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>46057</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46108</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45407</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45929</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45834</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>46052</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>46058</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44543</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45393</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45159</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45912</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46267</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45909</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44846</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45415</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>46036</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46003</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>46057</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>46031</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45902</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45362</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44519</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44473</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45522</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>46286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>46142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45630</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44923</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45804</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44522</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>46167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>46079</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>46238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>46057</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45968</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45987</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45834</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45895</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>46272</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>46238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44828</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44472</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45365</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45448</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>46134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45173</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>46283</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>46287</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>46287</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>44830</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45800</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>46135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45511</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>46057</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>46189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45511</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>46202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>46254</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46212</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45547</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>46236</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45786</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45343</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>46127</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45817</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45841</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>46195</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45502</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45426</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>46121</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44473</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>46196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45496</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45404</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>46106</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44516</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44881</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46127</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>45989</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45993</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45153</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>46002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44873</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45853</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45770</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>46177</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46189</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45572</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45432</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45181</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46261</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>46266</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>46223</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46233</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46248</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>46246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45786</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>44629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44575</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45684</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>44662</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44754</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>44810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44471</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44651</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>44755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44519</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>44477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>44817</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44873</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>44504</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44846</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>44467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44538</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44865</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44477</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44484</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44477</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44539</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>44536</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>44607</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>44816</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44547</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44844</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45310</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45229</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45420</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45477</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45477</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45114</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45545</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45512</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45702</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>46014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44844</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44476</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44894</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45453</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45588</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>46029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45330</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>46029</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>46029</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45488</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45488</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>46035</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45887</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45357</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>46038</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46038</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>46038</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46038</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45548</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>46038</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>46038</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46041</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>46042</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44873</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46043</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46044</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46043</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>46043</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44526</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45898</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45770</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45646</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45665</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45911</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>46057</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46062</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>46062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46062</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>46062</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>44874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45491</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45516</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45919</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46066</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44865</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46071</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45572</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46073</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45212</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45572</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45335</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45929</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46078</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45931</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45709</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45674</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46085</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45933</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45233</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>46100</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45812</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45950</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45950</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45950</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45952</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45952</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45952</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45952</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45953</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45348</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46112</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46112</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44916</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46127</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45968</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46127</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45350</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45974</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45114</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45986</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45988</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44755</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45988</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45660</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45722</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45722</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45992</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45322</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45994</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45201</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45076</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45996</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44978</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45901</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>44820</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>44859</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45709</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46006</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>44473</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>46003</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45679</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>46009</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>45048</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>46013</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45337</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45630</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45110</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46037</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46079</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44533</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45589</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45709</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46043</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>46148</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>46148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>46148</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>44911</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45830</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46149</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>46149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>46149</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>44754</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45253</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46154</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45113</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45015</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44495</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44963</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45848</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>45848</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45113</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45310</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45310</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45863</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45925</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45335</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>44505</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>46174</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44558</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>46052</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>46174</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>46174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>46030</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45415</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>46177</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45141</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45034</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45874</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45201</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45120</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45875</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45114</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>44568</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45638</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45665</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45665</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>44558</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45491</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44643</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45456</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45456</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>46252</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45404</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>45240</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45240</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>46211</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>46258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>46258</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45210</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45700</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>46258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>46258</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45693</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>46259</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45456</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>46083</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45153</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>46260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>46262</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>46261</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>46261</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45114</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>46262</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>46262</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>46262</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>46261</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45322</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47560,7 +47560,7 @@
         <v>45159</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45303</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45537</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45336</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>46268</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>44839</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>44526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45484</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>46269</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>46269</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45322</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46041</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>46231</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>46231</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45204</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45507</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>46276</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>46233</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45077</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45550</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>46236</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>46233</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45299</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45964</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45328</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>46233</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45691</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>45540</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46239</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45566</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>46286</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45327</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45560</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>44678</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>44910</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>44904</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>46112</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45247</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>46246</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>46288</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>46288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45175</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>46246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>44755</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>44496</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>46246</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45926</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>45597</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45356</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45575</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46246</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45106</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>44888</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45485</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>44873</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45254</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45477</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45584</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>44896</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45584</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>44651</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45274</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45322</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45322</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45700</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45307</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>45247</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45104</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45124</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45299</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45209</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45534</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45204</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45253</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45246</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45611</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45783</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>45783</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45539</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>45348</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53752,7 +53752,7 @@
         <v>45121</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45785</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>45432</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45441</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45223</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>44083</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>44637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54278,7 +54278,7 @@
         <v>44692</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>44692</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>44692</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>44715</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>44698</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>44602</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>44602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>44602</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>44662</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>44708</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>45357</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45355</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45356</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45684</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>45356</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45359</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45359</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45355</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45684</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>44806</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45359</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45357</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45357</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>45356</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45355</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45684</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45715</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45684</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45713</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45714</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>45758</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45757</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>45757</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45757</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45575</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45684</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>46089</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>46089</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57690,7 +57690,7 @@
         <v>46105</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>46104</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57846,7 +57846,7 @@
         <v>46104</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>46104</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>46150</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -643,19 +643,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="U2" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -666,11 +666,13 @@
 Gräddporing
 Gränsticka
 Gyllenspindling
+Rotfingersvamp
 Skrovlig taggsvamp
 Smalfotad taggsvamp
 Smultronkantarell
 Spadskinn
 Tajgataggsvamp
+Torrmusseron
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
@@ -761,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -912,7 +914,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1062,7 +1064,7 @@
         <v>46048</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1212,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1359,7 @@
         <v>46287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1499,7 +1501,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1641,7 +1643,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1779,7 +1781,7 @@
         <v>46272</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1917,7 +1919,7 @@
         <v>46255</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2055,7 +2057,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2191,7 +2193,7 @@
         <v>45901</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2332,7 +2334,7 @@
         <v>46252</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2468,7 +2470,7 @@
         <v>45700</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2603,7 +2605,7 @@
         <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2738,7 +2740,7 @@
         <v>45524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2867,7 +2869,7 @@
         <v>45110</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3001,7 +3003,7 @@
         <v>45502</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3130,7 +3132,7 @@
         <v>45833</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3255,7 +3257,7 @@
         <v>45825</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3389,7 +3391,7 @@
         <v>45926</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3522,7 +3524,7 @@
         <v>45960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3654,7 +3656,7 @@
         <v>45840</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3781,7 +3783,7 @@
         <v>45945</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3913,7 +3915,7 @@
         <v>45973</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4040,7 +4042,7 @@
         <v>45278</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4167,7 +4169,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4293,7 +4295,7 @@
         <v>46267</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4424,7 +4426,7 @@
         <v>46238</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4555,7 +4557,7 @@
         <v>45901</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4685,7 +4687,7 @@
         <v>45868</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4815,7 +4817,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4945,7 +4947,7 @@
         <v>45118</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5070,7 +5072,7 @@
         <v>46206</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5199,7 +5201,7 @@
         <v>45919</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5323,7 +5325,7 @@
         <v>46259</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5451,7 +5453,7 @@
         <v>45988</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5574,7 +5576,7 @@
         <v>45945</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5702,7 +5704,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5834,7 +5836,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5963,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6083,7 +6085,7 @@
         <v>44697</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6204,7 +6206,7 @@
         <v>45901</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6326,7 +6328,7 @@
         <v>46057</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6447,7 +6449,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6564,7 +6566,7 @@
         <v>46206</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6686,7 +6688,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6808,7 +6810,7 @@
         <v>46108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6934,7 +6936,7 @@
         <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7055,7 +7057,7 @@
         <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7181,7 +7183,7 @@
         <v>45929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7306,7 +7308,7 @@
         <v>45834</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7431,7 +7433,7 @@
         <v>45407</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7556,7 +7558,7 @@
         <v>46052</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7676,7 +7678,7 @@
         <v>46058</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7800,7 +7802,7 @@
         <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7903,7 +7905,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44936-2025</t>
+          <t>A 43867-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7917,10 +7919,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45918</v>
+        <v>45912</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7938,19 +7940,19 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>29.6</v>
+        <v>25.5</v>
       </c>
       <c r="J58" t="n">
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>7</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -7962,21 +7964,146 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
       </c>
       <c r="T58" t="n">
+        <v>155</v>
+      </c>
+      <c r="U58" t="n">
+        <v>155</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Doftskinn
+Kolflarnlav
+Mörk kolflarnlav
+Tallticka
+Talltita
+Vedflamlav
+Vedskivlav
+Plattlummer
+Spillkråka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 43867-2025 artfynd.xlsx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="X58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 43867-2025 karta.png", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="Y58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 43867-2025 georefererad karta.tif", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AA58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 43867-2025 FSC-klagomål.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AB58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 43867-2025 FSC-klagomål mail.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AC58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 43867-2025 tillsynsbegäran.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AD58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 43867-2025 tillsynsbegäran mail.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 43867-2025 prioriterade fågelarter.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 44936-2025</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>9</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" t="n">
+        <v>12</v>
+      </c>
+      <c r="T59" t="n">
         <v>288</v>
       </c>
-      <c r="U58" t="n">
+      <c r="U59" t="n">
         <v>288</v>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gräddporing
@@ -7992,116 +8119,116 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W58">
+      <c r="W59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 44936-2025 artfynd.xlsx", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="X58">
+      <c r="X59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 44936-2025 karta.png", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="Y58">
+      <c r="Y59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 44936-2025 georefererad karta.tif", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="AA58">
+      <c r="AA59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 44936-2025 FSC-klagomål.docx", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="AB58">
+      <c r="AB59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 44936-2025 FSC-klagomål mail.docx", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="AC58">
+      <c r="AC59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 44936-2025 tillsynsbegäran.docx", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="AD58">
+      <c r="AD59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 44936-2025 tillsynsbegäran mail.docx", "A 44936-2025")</f>
         <v/>
       </c>
-      <c r="AE58">
+      <c r="AE59">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 44936-2025 prioriterade fågelarter.docx", "A 44936-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>A 14277-2024</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="D60" s="1" t="n">
         <v>45393</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="E60" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I60" t="n">
         <v>2.8</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J60" t="n">
         <v>3</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K60" t="n">
         <v>1</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L60" t="n">
         <v>9</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M60" t="n">
         <v>1</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
         <v>10</v>
       </c>
-      <c r="R59" t="n">
+      <c r="R60" t="n">
         <v>1</v>
       </c>
-      <c r="S59" t="n">
+      <c r="S60" t="n">
         <v>12</v>
       </c>
-      <c r="T59" t="n">
+      <c r="T60" t="n">
         <v>94</v>
       </c>
-      <c r="U59" t="n">
+      <c r="U60" t="n">
         <v>88</v>
       </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blå taggsvamp
@@ -8117,111 +8244,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W59">
+      <c r="W60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 14277-2024 artfynd.xlsx", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="X59">
+      <c r="X60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 14277-2024 karta.png", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="Y59">
+      <c r="Y60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 14277-2024 georefererad karta.tif", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="AA59">
+      <c r="AA60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 14277-2024 FSC-klagomål.docx", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="AB59">
+      <c r="AB60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 14277-2024 FSC-klagomål mail.docx", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="AC59">
+      <c r="AC60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 14277-2024 tillsynsbegäran.docx", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="AD59">
+      <c r="AD60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 14277-2024 tillsynsbegäran mail.docx", "A 14277-2024")</f>
         <v/>
       </c>
-      <c r="AE59">
+      <c r="AE60">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 14277-2024 prioriterade fågelarter.docx", "A 14277-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>A 55982-2025</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D61" s="1" t="n">
         <v>45973</v>
       </c>
-      <c r="E60" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
+      <c r="E61" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J61" t="n">
         <v>4</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K61" t="n">
         <v>2</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L61" t="n">
         <v>6</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M61" t="n">
         <v>1</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>7</v>
       </c>
-      <c r="R60" t="n">
+      <c r="R61" t="n">
         <v>1</v>
       </c>
-      <c r="S60" t="n">
+      <c r="S61" t="n">
         <v>12</v>
       </c>
-      <c r="T60" t="n">
+      <c r="T61" t="n">
         <v>135</v>
       </c>
-      <c r="U60" t="n">
+      <c r="U61" t="n">
         <v>135</v>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blågrå svartspik
@@ -8237,116 +8364,116 @@
 Orre</t>
         </is>
       </c>
-      <c r="W60">
+      <c r="W61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 55982-2025 artfynd.xlsx", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="X60">
+      <c r="X61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 55982-2025 karta.png", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="Y60">
+      <c r="Y61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 55982-2025 georefererad karta.tif", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="AA60">
+      <c r="AA61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 55982-2025 FSC-klagomål.docx", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="AB60">
+      <c r="AB61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 55982-2025 FSC-klagomål mail.docx", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="AC60">
+      <c r="AC61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 55982-2025 tillsynsbegäran.docx", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="AD60">
+      <c r="AD61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 55982-2025 tillsynsbegäran mail.docx", "A 55982-2025")</f>
         <v/>
       </c>
-      <c r="AE60">
+      <c r="AE61">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 55982-2025 prioriterade fågelarter.docx", "A 55982-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>A 49247-2025</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D61" s="1" t="n">
+      <c r="D62" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="E61" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="E62" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="I62" t="n">
         <v>19</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J62" t="n">
         <v>3</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K62" t="n">
         <v>1</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L62" t="n">
         <v>8</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M62" t="n">
         <v>1</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>9</v>
       </c>
-      <c r="R61" t="n">
+      <c r="R62" t="n">
         <v>1</v>
       </c>
-      <c r="S61" t="n">
+      <c r="S62" t="n">
         <v>12</v>
       </c>
-      <c r="T61" t="n">
+      <c r="T62" t="n">
         <v>170</v>
       </c>
-      <c r="U61" t="n">
+      <c r="U62" t="n">
         <v>170</v>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Doftskinn
@@ -8362,111 +8489,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W61">
+      <c r="W62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 49247-2025 artfynd.xlsx", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="X61">
+      <c r="X62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 49247-2025 karta.png", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="Y61">
+      <c r="Y62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 49247-2025 georefererad karta.tif", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="AA61">
+      <c r="AA62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 49247-2025 FSC-klagomål.docx", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="AB61">
+      <c r="AB62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 49247-2025 FSC-klagomål mail.docx", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="AC61">
+      <c r="AC62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 49247-2025 tillsynsbegäran.docx", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="AD61">
+      <c r="AD62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 49247-2025 tillsynsbegäran mail.docx", "A 49247-2025")</f>
         <v/>
       </c>
-      <c r="AE61">
+      <c r="AE62">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 49247-2025 prioriterade fågelarter.docx", "A 49247-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>A 37730-2023</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D62" s="1" t="n">
+      <c r="D63" s="1" t="n">
         <v>45159</v>
       </c>
-      <c r="E62" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
+      <c r="E63" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
         <v>5.4</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J63" t="n">
         <v>4</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K63" t="n">
         <v>2</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L63" t="n">
         <v>6</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M63" t="n">
         <v>2</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
         <v>8</v>
       </c>
-      <c r="R62" t="n">
+      <c r="R63" t="n">
         <v>2</v>
       </c>
-      <c r="S62" t="n">
+      <c r="S63" t="n">
         <v>12</v>
       </c>
-      <c r="T62" t="n">
+      <c r="T63" t="n">
         <v>63</v>
       </c>
-      <c r="U62" t="n">
+      <c r="U63" t="n">
         <v>63</v>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -8482,164 +8609,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W62">
+      <c r="W63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 37730-2023 artfynd.xlsx", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="X62">
+      <c r="X63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 37730-2023 karta.png", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="Y62">
+      <c r="Y63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 37730-2023 georefererad karta.tif", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="Z62">
+      <c r="Z63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/knärot/A 37730-2023 karta knärot.png", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="AA62">
+      <c r="AA63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 37730-2023 FSC-klagomål.docx", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="AB62">
+      <c r="AB63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 37730-2023 FSC-klagomål mail.docx", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="AC62">
+      <c r="AC63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 37730-2023 tillsynsbegäran.docx", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="AD62">
+      <c r="AD63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 37730-2023 tillsynsbegäran mail.docx", "A 37730-2023")</f>
         <v/>
       </c>
-      <c r="AE62">
+      <c r="AE63">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 37730-2023 prioriterade fågelarter.docx", "A 37730-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>A 43867-2025</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E63" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>6</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>7</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>11</v>
-      </c>
-      <c r="T63" t="n">
-        <v>132</v>
-      </c>
-      <c r="U63" t="n">
-        <v>132</v>
-      </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Doftskinn
-Kolflarnlav
-Mörk kolflarnlav
-Talltita
-Vedflamlav
-Vedskivlav
-Plattlummer
-Spillkråka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 43867-2025 artfynd.xlsx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 43867-2025 karta.png", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 43867-2025 georefererad karta.tif", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 43867-2025 FSC-klagomål.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 43867-2025 FSC-klagomål mail.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 43867-2025 tillsynsbegäran.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 43867-2025 tillsynsbegäran mail.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AE63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 43867-2025 prioriterade fågelarter.docx", "A 43867-2025")</f>
         <v/>
       </c>
     </row>
@@ -8663,7 +8666,7 @@
         <v>46267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8787,7 +8790,7 @@
         <v>45891</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8906,7 +8909,7 @@
         <v>45909</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9025,7 +9028,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9149,7 +9152,7 @@
         <v>44846</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9271,7 +9274,7 @@
         <v>46003</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9389,7 +9392,7 @@
         <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9508,7 +9511,7 @@
         <v>46036</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9631,7 +9634,7 @@
         <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9750,7 +9753,7 @@
         <v>45792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9873,7 +9876,7 @@
         <v>46057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9991,7 +9994,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10109,7 +10112,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10232,7 +10235,7 @@
         <v>45748</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10350,7 +10353,7 @@
         <v>45891</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10468,7 +10471,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10586,7 +10589,7 @@
         <v>45415</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10709,7 +10712,7 @@
         <v>44473</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10826,7 +10829,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10944,7 +10947,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11062,7 +11065,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11179,7 +11182,7 @@
         <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11301,7 +11304,7 @@
         <v>45362</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11419,7 +11422,7 @@
         <v>45630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11541,7 +11544,7 @@
         <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11663,7 +11666,7 @@
         <v>46142</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11785,7 +11788,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11903,7 +11906,7 @@
         <v>44519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12021,7 +12024,7 @@
         <v>45522</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12138,7 +12141,7 @@
         <v>46008</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12254,7 +12257,7 @@
         <v>45593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12374,7 +12377,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12486,7 +12489,7 @@
         <v>45804</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12607,7 +12610,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12723,7 +12726,7 @@
         <v>44522</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12843,7 +12846,7 @@
         <v>46167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12963,7 +12966,7 @@
         <v>45600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13084,7 +13087,7 @@
         <v>46079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13200,7 +13203,7 @@
         <v>44923</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13320,7 +13323,7 @@
         <v>46238</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13441,7 +13444,7 @@
         <v>45943</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13562,7 +13565,7 @@
         <v>45988</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13683,7 +13686,7 @@
         <v>45210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13799,7 +13802,7 @@
         <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13919,7 +13922,7 @@
         <v>45162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14035,7 +14038,7 @@
         <v>46057</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14150,7 +14153,7 @@
         <v>45968</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14266,7 +14269,7 @@
         <v>45987</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14382,7 +14385,7 @@
         <v>45834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14498,7 +14501,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14613,7 +14616,7 @@
         <v>46238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14733,7 +14736,7 @@
         <v>44602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14853,7 +14856,7 @@
         <v>44828</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14964,7 +14967,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15084,7 +15087,7 @@
         <v>44472</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15194,7 +15197,7 @@
         <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15309,7 +15312,7 @@
         <v>45365</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15427,7 +15430,7 @@
         <v>45804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15546,7 +15549,7 @@
         <v>46134</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15660,7 +15663,7 @@
         <v>45841</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15775,7 +15778,7 @@
         <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15890,7 +15893,7 @@
         <v>45448</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16005,7 +16008,7 @@
         <v>45210</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16120,7 +16123,7 @@
         <v>45902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16238,7 +16241,7 @@
         <v>45511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16352,7 +16355,7 @@
         <v>45799</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16466,7 +16469,7 @@
         <v>45173</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16584,7 +16587,7 @@
         <v>45225</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16702,7 +16705,7 @@
         <v>46202</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16815,7 +16818,7 @@
         <v>46283</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16933,7 +16936,7 @@
         <v>45755</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17047,7 +17050,7 @@
         <v>45432</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17161,7 +17164,7 @@
         <v>45462</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17275,7 +17278,7 @@
         <v>46121</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17389,7 +17392,7 @@
         <v>45786</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17502,7 +17505,7 @@
         <v>45078</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17615,7 +17618,7 @@
         <v>45800</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17728,7 +17731,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17841,7 +17844,7 @@
         <v>45182</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17954,7 +17957,7 @@
         <v>46135</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18067,7 +18070,7 @@
         <v>45537</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18180,7 +18183,7 @@
         <v>45547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18293,7 +18296,7 @@
         <v>45638</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18406,7 +18409,7 @@
         <v>46057</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18518,7 +18521,7 @@
         <v>46189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18631,7 +18634,7 @@
         <v>46202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18743,7 +18746,7 @@
         <v>44830</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18860,7 +18863,7 @@
         <v>45511</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18973,7 +18976,7 @@
         <v>46212</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19081,7 +19084,7 @@
         <v>46212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19189,7 +19192,7 @@
         <v>45511</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19302,7 +19305,7 @@
         <v>46236</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19419,7 +19422,7 @@
         <v>46254</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19532,7 +19535,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19644,7 +19647,7 @@
         <v>45343</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19756,7 +19759,7 @@
         <v>45426</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19868,7 +19871,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19980,7 +19983,7 @@
         <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20096,7 +20099,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20208,7 +20211,7 @@
         <v>45985</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20324,7 +20327,7 @@
         <v>45992</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20436,7 +20439,7 @@
         <v>46127</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20543,7 +20546,7 @@
         <v>45841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20655,7 +20658,7 @@
         <v>45502</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20767,7 +20770,7 @@
         <v>46195</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20879,7 +20882,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20991,7 +20994,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21102,7 +21105,7 @@
         <v>44706</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21213,7 +21216,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21319,7 +21322,7 @@
         <v>45817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21430,7 +21433,7 @@
         <v>44473</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21536,7 +21539,7 @@
         <v>45968</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21647,7 +21650,7 @@
         <v>45968</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21758,7 +21761,7 @@
         <v>46121</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21873,7 +21876,7 @@
         <v>45833</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21988,7 +21991,7 @@
         <v>45404</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22094,7 +22097,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22205,7 +22208,7 @@
         <v>45895</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22315,7 +22318,7 @@
         <v>46196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22426,7 +22429,7 @@
         <v>46265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22537,7 +22540,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22648,7 +22651,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22758,7 +22761,7 @@
         <v>45575</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22868,7 +22871,7 @@
         <v>44874</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22974,7 +22977,7 @@
         <v>45902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23085,7 +23088,7 @@
         <v>46106</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23200,7 +23203,7 @@
         <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23311,7 +23314,7 @@
         <v>44516</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23421,7 +23424,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23531,7 +23534,7 @@
         <v>45786</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23641,7 +23644,7 @@
         <v>46002</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23751,7 +23754,7 @@
         <v>45432</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23861,7 +23864,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23971,7 +23974,7 @@
         <v>46058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24080,7 +24083,7 @@
         <v>45181</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24185,7 +24188,7 @@
         <v>45938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24295,7 +24298,7 @@
         <v>45502</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24404,7 +24407,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24514,7 +24517,7 @@
         <v>45153</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24623,7 +24626,7 @@
         <v>45989</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24733,7 +24736,7 @@
         <v>45993</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24838,7 +24841,7 @@
         <v>45512</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24948,7 +24951,7 @@
         <v>46127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25058,7 +25061,7 @@
         <v>45853</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25168,7 +25171,7 @@
         <v>44881</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25278,7 +25281,7 @@
         <v>45770</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25388,7 +25391,7 @@
         <v>45572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25502,7 +25505,7 @@
         <v>46177</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25612,7 +25615,7 @@
         <v>46189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25722,7 +25725,7 @@
         <v>45792</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25827,7 +25830,7 @@
         <v>44873</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25937,7 +25940,7 @@
         <v>46261</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26042,7 +26045,7 @@
         <v>46223</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26151,7 +26154,7 @@
         <v>46266</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26265,7 +26268,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26375,7 +26378,7 @@
         <v>46233</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26480,7 +26483,7 @@
         <v>46246</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26585,7 +26588,7 @@
         <v>46248</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26695,7 +26698,7 @@
         <v>45511</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26805,7 +26808,7 @@
         <v>44629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26919,7 +26922,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27029,7 +27032,7 @@
         <v>44575</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27143,7 +27146,7 @@
         <v>45903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27253,7 +27256,7 @@
         <v>44662</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27326,7 +27329,7 @@
         <v>44754</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27399,7 +27402,7 @@
         <v>44810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27477,7 +27480,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27550,7 +27553,7 @@
         <v>44651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27623,7 +27626,7 @@
         <v>44755</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27696,7 +27699,7 @@
         <v>44519</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27774,7 +27777,7 @@
         <v>44477</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27852,7 +27855,7 @@
         <v>44552</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27930,7 +27933,7 @@
         <v>44873</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28003,7 +28006,7 @@
         <v>44817</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28081,7 +28084,7 @@
         <v>44504</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28159,7 +28162,7 @@
         <v>44846</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28232,7 +28235,7 @@
         <v>44538</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28310,7 +28313,7 @@
         <v>44865</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28388,7 +28391,7 @@
         <v>44697</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28461,7 +28464,7 @@
         <v>44477</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28539,7 +28542,7 @@
         <v>44501</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28612,7 +28615,7 @@
         <v>44705</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28685,7 +28688,7 @@
         <v>44484</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28758,7 +28761,7 @@
         <v>44477</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28831,7 +28834,7 @@
         <v>44732</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28909,7 +28912,7 @@
         <v>44539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28982,7 +28985,7 @@
         <v>44536</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29060,7 +29063,7 @@
         <v>44680</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29138,7 +29141,7 @@
         <v>44607</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29211,7 +29214,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29289,7 +29292,7 @@
         <v>44636</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29362,7 +29365,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29440,7 +29443,7 @@
         <v>44547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29518,7 +29521,7 @@
         <v>45456</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29591,7 +29594,7 @@
         <v>44476</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29664,7 +29667,7 @@
         <v>45534</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29737,7 +29740,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29810,7 +29813,7 @@
         <v>45097</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29888,7 +29891,7 @@
         <v>44558</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29961,7 +29964,7 @@
         <v>44526</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30039,7 +30042,7 @@
         <v>45307</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30112,7 +30115,7 @@
         <v>45307</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30185,7 +30188,7 @@
         <v>45210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30258,7 +30261,7 @@
         <v>46001</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30331,7 +30334,7 @@
         <v>44526</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30409,7 +30412,7 @@
         <v>45887</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30487,7 +30490,7 @@
         <v>45246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30560,7 +30563,7 @@
         <v>45357</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30638,7 +30641,7 @@
         <v>46003</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30711,7 +30714,7 @@
         <v>45491</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30784,7 +30787,7 @@
         <v>46006</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30857,7 +30860,7 @@
         <v>45247</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30930,7 +30933,7 @@
         <v>46009</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31003,7 +31006,7 @@
         <v>45223</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31076,7 +31079,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31149,7 +31152,7 @@
         <v>46014</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31222,7 +31225,7 @@
         <v>45477</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31295,7 +31298,7 @@
         <v>45477</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31368,7 +31371,7 @@
         <v>44568</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31441,7 +31444,7 @@
         <v>45210</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31519,7 +31522,7 @@
         <v>46029</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31592,7 +31595,7 @@
         <v>46029</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31665,7 +31668,7 @@
         <v>46029</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31738,7 +31741,7 @@
         <v>46030</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31811,7 +31814,7 @@
         <v>45488</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31884,7 +31887,7 @@
         <v>45898</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31957,7 +31960,7 @@
         <v>46035</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32035,7 +32038,7 @@
         <v>46031</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32113,7 +32116,7 @@
         <v>46041</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32186,7 +32189,7 @@
         <v>46041</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32259,7 +32262,7 @@
         <v>46038</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32332,7 +32335,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32405,7 +32408,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32478,7 +32481,7 @@
         <v>46038</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32551,7 +32554,7 @@
         <v>46038</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32624,7 +32627,7 @@
         <v>46038</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32697,7 +32700,7 @@
         <v>46038</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32770,7 +32773,7 @@
         <v>46038</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32843,7 +32846,7 @@
         <v>46043</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32916,7 +32919,7 @@
         <v>46043</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32989,7 +32992,7 @@
         <v>45911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33062,7 +33065,7 @@
         <v>46043</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33135,7 +33138,7 @@
         <v>45545</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33208,7 +33211,7 @@
         <v>46043</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33281,7 +33284,7 @@
         <v>45335</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33354,7 +33357,7 @@
         <v>45911</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33432,7 +33435,7 @@
         <v>45588</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33505,7 +33508,7 @@
         <v>46042</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33578,7 +33581,7 @@
         <v>45453</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33651,7 +33654,7 @@
         <v>45911</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33724,7 +33727,7 @@
         <v>45770</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33802,7 +33805,7 @@
         <v>46044</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33875,7 +33878,7 @@
         <v>45253</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33948,7 +33951,7 @@
         <v>45798</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34021,7 +34024,7 @@
         <v>45800</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34099,7 +34102,7 @@
         <v>44755</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34177,7 +34180,7 @@
         <v>45572</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34255,7 +34258,7 @@
         <v>45919</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34333,7 +34336,7 @@
         <v>44865</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34411,7 +34414,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34489,7 +34492,7 @@
         <v>45693</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34562,7 +34565,7 @@
         <v>46057</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34635,7 +34638,7 @@
         <v>45929</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34713,7 +34716,7 @@
         <v>44839</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34786,7 +34789,7 @@
         <v>45926</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34864,7 +34867,7 @@
         <v>45929</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34942,7 +34945,7 @@
         <v>45548</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35015,7 +35018,7 @@
         <v>46062</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35088,7 +35091,7 @@
         <v>46062</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35161,7 +35164,7 @@
         <v>45931</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35234,7 +35237,7 @@
         <v>46062</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35307,7 +35310,7 @@
         <v>46062</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35380,7 +35383,7 @@
         <v>45322</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35453,7 +35456,7 @@
         <v>45322</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35526,7 +35529,7 @@
         <v>45322</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35599,7 +35602,7 @@
         <v>45931</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35672,7 +35675,7 @@
         <v>46062</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35745,7 +35748,7 @@
         <v>45491</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35818,7 +35821,7 @@
         <v>44904</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35891,7 +35894,7 @@
         <v>45679</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35964,7 +35967,7 @@
         <v>45933</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36037,7 +36040,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36110,7 +36113,7 @@
         <v>45015</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36183,7 +36186,7 @@
         <v>45674</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36256,7 +36259,7 @@
         <v>46071</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36329,7 +36332,7 @@
         <v>46071</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36402,7 +36405,7 @@
         <v>46073</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36475,7 +36478,7 @@
         <v>45597</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36548,7 +36551,7 @@
         <v>46078</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36621,7 +36624,7 @@
         <v>45335</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36694,7 +36697,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36772,7 +36775,7 @@
         <v>45950</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36845,7 +36848,7 @@
         <v>45950</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36918,7 +36921,7 @@
         <v>45950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36996,7 +36999,7 @@
         <v>45953</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37074,7 +37077,7 @@
         <v>45952</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37152,7 +37155,7 @@
         <v>45952</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37230,7 +37233,7 @@
         <v>44873</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37303,7 +37306,7 @@
         <v>45952</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37381,7 +37384,7 @@
         <v>45952</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37459,7 +37462,7 @@
         <v>46085</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37532,7 +37535,7 @@
         <v>45812</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37610,7 +37613,7 @@
         <v>45350</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37688,7 +37691,7 @@
         <v>45964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37766,7 +37769,7 @@
         <v>44820</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37839,7 +37842,7 @@
         <v>45566</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37917,7 +37920,7 @@
         <v>44505</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37995,7 +37998,7 @@
         <v>45299</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38068,7 +38071,7 @@
         <v>44473</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38165,7 +38168,7 @@
         <v>45310</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38238,7 +38241,7 @@
         <v>45310</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38311,7 +38314,7 @@
         <v>45968</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38389,7 +38392,7 @@
         <v>45175</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38462,7 +38465,7 @@
         <v>45665</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38535,7 +38538,7 @@
         <v>45973</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38613,7 +38616,7 @@
         <v>45973</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38691,7 +38694,7 @@
         <v>44888</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38764,7 +38767,7 @@
         <v>46100</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38837,7 +38840,7 @@
         <v>45974</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38910,7 +38913,7 @@
         <v>45322</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38983,7 +38986,7 @@
         <v>45201</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39061,7 +39064,7 @@
         <v>45646</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39134,7 +39137,7 @@
         <v>45336</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39207,7 +39210,7 @@
         <v>45299</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39280,7 +39283,7 @@
         <v>45233</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39358,7 +39361,7 @@
         <v>46107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39436,7 +39439,7 @@
         <v>45980</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39509,7 +39512,7 @@
         <v>45310</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39582,7 +39585,7 @@
         <v>46112</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39655,7 +39658,7 @@
         <v>46112</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39728,7 +39731,7 @@
         <v>45986</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39806,7 +39809,7 @@
         <v>45988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39879,7 +39882,7 @@
         <v>45700</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39957,7 +39960,7 @@
         <v>45988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40030,7 +40033,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40103,7 +40106,7 @@
         <v>45722</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40181,7 +40184,7 @@
         <v>45722</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40259,7 +40262,7 @@
         <v>45992</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40337,7 +40340,7 @@
         <v>45992</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40415,7 +40418,7 @@
         <v>45992</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40493,7 +40496,7 @@
         <v>45560</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40571,7 +40574,7 @@
         <v>45994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40649,7 +40652,7 @@
         <v>44911</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40722,7 +40725,7 @@
         <v>45996</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40795,7 +40798,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40868,7 +40871,7 @@
         <v>45512</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40946,7 +40949,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41019,7 +41022,7 @@
         <v>45830</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41092,7 +41095,7 @@
         <v>45159</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41170,7 +41173,7 @@
         <v>45274</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41243,7 +41246,7 @@
         <v>45484</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41316,7 +41319,7 @@
         <v>45477</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41389,7 +41392,7 @@
         <v>45322</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41462,7 +41465,7 @@
         <v>45901</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41535,7 +41538,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41608,7 +41611,7 @@
         <v>45630</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41681,7 +41684,7 @@
         <v>45691</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41759,7 +41762,7 @@
         <v>45665</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41832,7 +41835,7 @@
         <v>45848</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41905,7 +41908,7 @@
         <v>45420</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41983,7 +41986,7 @@
         <v>46037</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42056,7 +42059,7 @@
         <v>45863</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42134,7 +42137,7 @@
         <v>45638</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42212,7 +42215,7 @@
         <v>45254</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42285,7 +42288,7 @@
         <v>45415</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42358,7 +42361,7 @@
         <v>45589</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42431,7 +42434,7 @@
         <v>45709</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42509,7 +42512,7 @@
         <v>46079</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42582,7 +42585,7 @@
         <v>45356</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42655,7 +42658,7 @@
         <v>44904</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42728,7 +42731,7 @@
         <v>46043</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42801,7 +42804,7 @@
         <v>45212</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42879,7 +42882,7 @@
         <v>45209</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42952,7 +42955,7 @@
         <v>46148</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43025,7 +43028,7 @@
         <v>46149</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43103,7 +43106,7 @@
         <v>45141</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43176,7 +43179,7 @@
         <v>46149</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43254,7 +43257,7 @@
         <v>44844</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43332,7 +43335,7 @@
         <v>46148</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43405,7 +43408,7 @@
         <v>46148</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43478,7 +43481,7 @@
         <v>46149</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43556,7 +43559,7 @@
         <v>45106</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43629,7 +43632,7 @@
         <v>46153</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43702,7 +43705,7 @@
         <v>44896</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43780,7 +43783,7 @@
         <v>45077</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43853,7 +43856,7 @@
         <v>45874</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43931,7 +43934,7 @@
         <v>46154</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44004,7 +44007,7 @@
         <v>44754</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44077,7 +44080,7 @@
         <v>45875</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44150,7 +44153,7 @@
         <v>44678</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44223,7 +44226,7 @@
         <v>45076</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44296,7 +44299,7 @@
         <v>45485</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44369,7 +44372,7 @@
         <v>45246</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44442,7 +44445,7 @@
         <v>45124</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44515,7 +44518,7 @@
         <v>46168</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44593,7 +44596,7 @@
         <v>44859</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44671,7 +44674,7 @@
         <v>46052</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44744,7 +44747,7 @@
         <v>45114</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44817,7 +44820,7 @@
         <v>46174</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44890,7 +44893,7 @@
         <v>46174</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44963,7 +44966,7 @@
         <v>46174</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45036,7 +45039,7 @@
         <v>46174</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45109,7 +45112,7 @@
         <v>45925</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45182,7 +45185,7 @@
         <v>45550</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45255,7 +45258,7 @@
         <v>46030</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45328,7 +45331,7 @@
         <v>46177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45401,7 +45404,7 @@
         <v>44558</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45474,7 +45477,7 @@
         <v>44495</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45552,7 +45555,7 @@
         <v>44651</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45630,7 +45633,7 @@
         <v>45456</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45703,7 +45706,7 @@
         <v>45456</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45776,7 +45779,7 @@
         <v>45327</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45849,7 +45852,7 @@
         <v>45110</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45927,7 +45930,7 @@
         <v>45072</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46005,7 +46008,7 @@
         <v>45638</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46083,7 +46086,7 @@
         <v>45665</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46156,7 +46159,7 @@
         <v>45700</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46229,7 +46232,7 @@
         <v>45584</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46302,7 +46305,7 @@
         <v>44755</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46375,7 +46378,7 @@
         <v>44873</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46448,7 +46451,7 @@
         <v>45240</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46526,7 +46529,7 @@
         <v>45240</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46604,7 +46607,7 @@
         <v>45247</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46677,7 +46680,7 @@
         <v>46211</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46750,7 +46753,7 @@
         <v>44844</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46823,7 +46826,7 @@
         <v>46258</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46896,7 +46899,7 @@
         <v>46258</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46969,7 +46972,7 @@
         <v>46083</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47042,7 +47045,7 @@
         <v>46259</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47120,7 +47123,7 @@
         <v>46258</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47193,7 +47196,7 @@
         <v>46258</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47266,7 +47269,7 @@
         <v>46261</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47344,7 +47347,7 @@
         <v>45588</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47417,7 +47420,7 @@
         <v>46260</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47490,7 +47493,7 @@
         <v>45204</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47563,7 +47566,7 @@
         <v>46261</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47636,7 +47639,7 @@
         <v>46261</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47709,7 +47712,7 @@
         <v>45507</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47782,7 +47785,7 @@
         <v>46262</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47855,7 +47858,7 @@
         <v>46262</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47928,7 +47931,7 @@
         <v>46262</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48001,7 +48004,7 @@
         <v>45328</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48074,7 +48077,7 @@
         <v>45537</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48147,7 +48150,7 @@
         <v>46262</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48220,7 +48223,7 @@
         <v>44978</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48293,7 +48296,7 @@
         <v>46269</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48366,7 +48369,7 @@
         <v>46269</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48439,7 +48442,7 @@
         <v>46268</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48512,7 +48515,7 @@
         <v>44874</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48585,7 +48588,7 @@
         <v>46041</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48658,7 +48661,7 @@
         <v>45104</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48736,7 +48739,7 @@
         <v>46231</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48814,7 +48817,7 @@
         <v>46231</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48892,7 +48895,7 @@
         <v>46276</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48970,7 +48973,7 @@
         <v>46233</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49048,7 +49051,7 @@
         <v>46233</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49126,7 +49129,7 @@
         <v>46236</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49204,7 +49207,7 @@
         <v>46233</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49282,7 +49285,7 @@
         <v>45113</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49360,7 +49363,7 @@
         <v>45114</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49433,7 +49436,7 @@
         <v>45113</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49511,7 +49514,7 @@
         <v>45964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49584,7 +49587,7 @@
         <v>45114</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49657,7 +49660,7 @@
         <v>46239</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49735,7 +49738,7 @@
         <v>45540</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49808,7 +49811,7 @@
         <v>45404</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49881,7 +49884,7 @@
         <v>45660</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49959,7 +49962,7 @@
         <v>46286</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50037,7 +50040,7 @@
         <v>45120</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50110,7 +50113,7 @@
         <v>46246</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50183,7 +50186,7 @@
         <v>46246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50256,7 +50259,7 @@
         <v>45201</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50334,7 +50337,7 @@
         <v>46246</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50407,7 +50410,7 @@
         <v>44904</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50480,7 +50483,7 @@
         <v>46112</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50553,7 +50556,7 @@
         <v>46246</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50626,7 +50629,7 @@
         <v>46288</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50699,7 +50702,7 @@
         <v>46288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50772,7 +50775,7 @@
         <v>45253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50845,7 +50848,7 @@
         <v>45575</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50918,7 +50921,7 @@
         <v>45114</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50991,7 +50994,7 @@
         <v>44916</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51064,7 +51067,7 @@
         <v>45611</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51137,7 +51140,7 @@
         <v>45337</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51210,7 +51213,7 @@
         <v>44894</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51283,7 +51286,7 @@
         <v>45204</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51356,7 +51359,7 @@
         <v>46294</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51429,7 +51432,7 @@
         <v>44963</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51502,7 +51505,7 @@
         <v>46296</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51575,7 +51578,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51648,7 +51651,7 @@
         <v>46296</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51726,7 +51729,7 @@
         <v>45926</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51832,7 +51835,7 @@
         <v>46252</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51905,7 +51908,7 @@
         <v>45229</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51978,7 +51981,7 @@
         <v>44533</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52051,7 +52054,7 @@
         <v>45114</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52129,7 +52132,7 @@
         <v>45303</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52202,7 +52205,7 @@
         <v>44916</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52275,7 +52278,7 @@
         <v>45204</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52348,7 +52351,7 @@
         <v>45330</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52421,7 +52424,7 @@
         <v>45702</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52499,7 +52502,7 @@
         <v>45516</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52572,7 +52575,7 @@
         <v>45584</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52645,7 +52648,7 @@
         <v>45488</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52718,7 +52721,7 @@
         <v>45175</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52791,7 +52794,7 @@
         <v>45153</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52864,7 +52867,7 @@
         <v>45048</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52937,7 +52940,7 @@
         <v>44643</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53015,7 +53018,7 @@
         <v>45572</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53093,7 +53096,7 @@
         <v>44910</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53166,7 +53169,7 @@
         <v>45709</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53239,7 +53242,7 @@
         <v>45709</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53312,7 +53315,7 @@
         <v>44742</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53390,7 +53393,7 @@
         <v>45107</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53463,7 +53466,7 @@
         <v>45034</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53536,7 +53539,7 @@
         <v>45348</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53609,7 +53612,7 @@
         <v>45310</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53682,7 +53685,7 @@
         <v>44496</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53760,7 +53763,7 @@
         <v>45783</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53833,7 +53836,7 @@
         <v>45783</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53906,7 +53909,7 @@
         <v>45539</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53979,7 +53982,7 @@
         <v>45785</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54057,7 +54060,7 @@
         <v>45432</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54130,7 +54133,7 @@
         <v>45441</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54203,7 +54206,7 @@
         <v>45121</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54276,7 +54279,7 @@
         <v>45348</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54349,7 +54352,7 @@
         <v>44637</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54427,7 +54430,7 @@
         <v>44083</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54505,7 +54508,7 @@
         <v>45357</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54583,7 +54586,7 @@
         <v>44692</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54661,7 +54664,7 @@
         <v>44692</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54739,7 +54742,7 @@
         <v>45355</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54817,7 +54820,7 @@
         <v>45356</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54895,7 +54898,7 @@
         <v>45684</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54973,7 +54976,7 @@
         <v>44692</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55051,7 +55054,7 @@
         <v>44715</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55129,7 +55132,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55207,7 +55210,7 @@
         <v>45359</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55285,7 +55288,7 @@
         <v>45359</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55363,7 +55366,7 @@
         <v>44698</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55441,7 +55444,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55519,7 +55522,7 @@
         <v>44602</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55597,7 +55600,7 @@
         <v>45355</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55675,7 +55678,7 @@
         <v>45684</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55753,7 +55756,7 @@
         <v>44806</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55826,7 +55829,7 @@
         <v>45356</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55904,7 +55907,7 @@
         <v>45359</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55982,7 +55985,7 @@
         <v>44602</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56060,7 +56063,7 @@
         <v>45357</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56138,7 +56141,7 @@
         <v>45357</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56216,7 +56219,7 @@
         <v>44602</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56294,7 +56297,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56372,7 +56375,7 @@
         <v>45356</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56450,7 +56453,7 @@
         <v>44662</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56523,7 +56526,7 @@
         <v>45355</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56601,7 +56604,7 @@
         <v>44708</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56679,7 +56682,7 @@
         <v>45684</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56757,7 +56760,7 @@
         <v>45715</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56830,7 +56833,7 @@
         <v>45684</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56908,7 +56911,7 @@
         <v>45713</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56986,7 +56989,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57064,7 +57067,7 @@
         <v>45757</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57142,7 +57145,7 @@
         <v>45757</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57220,7 +57223,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57298,7 +57301,7 @@
         <v>45757</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57376,7 +57379,7 @@
         <v>45758</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57454,7 +57457,7 @@
         <v>45575</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57527,7 +57530,7 @@
         <v>45684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57605,7 +57608,7 @@
         <v>46089</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57683,7 +57686,7 @@
         <v>46089</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57761,7 +57764,7 @@
         <v>46104</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57839,7 +57842,7 @@
         <v>46104</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57917,7 +57920,7 @@
         <v>46104</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57995,7 +57998,7 @@
         <v>46104</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -58073,7 +58076,7 @@
         <v>46104</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -58151,7 +58154,7 @@
         <v>46105</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -58229,7 +58232,7 @@
         <v>46150</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>46048</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>46272</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46255</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45901</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45988</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>46252</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45700</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45110</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45502</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45833</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45825</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>45945</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>46301</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45278</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36031-2026</t>
+          <t>A 43867-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46267</v>
+        <v>45912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4583,23 +4583,23 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>25.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4611,21 +4611,152 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>18</v>
       </c>
       <c r="T31" t="n">
+        <v>231</v>
+      </c>
+      <c r="U31" t="n">
+        <v>231</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Blanksvart spiklav
+Doftskinn
+Kolflarnlav
+Motaggsvamp
+Mörk kolflarnlav
+Skogshare
+Talltagel
+Tallticka
+Talltita
+Tretåig hackspett
+Vedflamlav
+Vedskivlav
+Violettgrå tagellav
+Plattlummer
+Spillkråka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 43867-2025 artfynd.xlsx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 43867-2025 karta.png", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 43867-2025 georefererad karta.tif", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 43867-2025 FSC-klagomål.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 43867-2025 FSC-klagomål mail.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 43867-2025 tillsynsbegäran.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 43867-2025 tillsynsbegäran mail.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 43867-2025 prioriterade fågelarter.docx", "A 43867-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 36031-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>18</v>
+      </c>
+      <c r="T32" t="n">
         <v>66</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gräddporing
@@ -4647,116 +4778,116 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 36031-2026 artfynd.xlsx", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 36031-2026 karta.png", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 36031-2026 georefererad karta.tif", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 36031-2026 FSC-klagomål.docx", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 36031-2026 FSC-klagomål mail.docx", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 36031-2026 tillsynsbegäran.docx", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 36031-2026 tillsynsbegäran mail.docx", "A 36031-2026")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 36031-2026 prioriterade fågelarter.docx", "A 36031-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 32395-2026</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>3.6</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>14</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>4</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>18</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>4</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>18</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>41</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>41</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Calicium ramboldiicola
 Fläckporing
@@ -4778,111 +4909,111 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 32395-2026 artfynd.xlsx", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 32395-2026 karta.png", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 32395-2026 georefererad karta.tif", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 32395-2026 FSC-klagomål.docx", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 32395-2026 FSC-klagomål mail.docx", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 32395-2026 tillsynsbegäran.docx", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 32395-2026 tillsynsbegäran mail.docx", "A 32395-2026")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 32395-2026 prioriterade fågelarter.docx", "A 32395-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 19109-2023</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>45044</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>202.7</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>9</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>12</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>13</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>18</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>56</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>56</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Björktrast
@@ -4904,111 +5035,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 19109-2023 artfynd.xlsx", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 19109-2023 karta.png", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 19109-2023 georefererad karta.tif", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 19109-2023 FSC-klagomål.docx", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 19109-2023 FSC-klagomål mail.docx", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 19109-2023 tillsynsbegäran.docx", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 19109-2023 tillsynsbegäran mail.docx", "A 19109-2023")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 19109-2023 prioriterade fågelarter.docx", "A 19109-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 33548-2023</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>5.2</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>9</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>4</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>6</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>7</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>17</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>55</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U35" t="n">
         <v>55</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Rosenticka
@@ -5029,116 +5160,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 33548-2023 artfynd.xlsx", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 33548-2023 karta.png", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 33548-2023 georefererad karta.tif", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 33548-2023 FSC-klagomål.docx", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 33548-2023 FSC-klagomål mail.docx", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 33548-2023 tillsynsbegäran.docx", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 33548-2023 tillsynsbegäran mail.docx", "A 33548-2023")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 33548-2023 prioriterade fågelarter.docx", "A 33548-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 41639-2025</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="E36" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>27.8</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>6</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>10</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M36" t="n">
         <v>2</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>12</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>2</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>17</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>233</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>213</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Spadskinn
@@ -5159,116 +5290,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 41639-2025 artfynd.xlsx", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 41639-2025 karta.png", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 41639-2025 georefererad karta.tif", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 41639-2025 FSC-klagomål.docx", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 41639-2025 FSC-klagomål mail.docx", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 41639-2025 tillsynsbegäran.docx", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 41639-2025 tillsynsbegäran mail.docx", "A 41639-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 41639-2025 prioriterade fågelarter.docx", "A 41639-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 36371-2025</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>45868</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="E37" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>30.8</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>2</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>11</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>12</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S37" t="n">
         <v>17</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>269</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>256</v>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blanksvart spiklav
@@ -5289,116 +5420,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 36371-2025 artfynd.xlsx", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 36371-2025 karta.png", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 36371-2025 georefererad karta.tif", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 36371-2025 FSC-klagomål.docx", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 36371-2025 FSC-klagomål mail.docx", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 36371-2025 tillsynsbegäran.docx", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 36371-2025 tillsynsbegäran mail.docx", "A 36371-2025")</f>
         <v/>
       </c>
-      <c r="AE36">
+      <c r="AE37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 36371-2025 prioriterade fågelarter.docx", "A 36371-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 26765-2025</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D38" s="1" t="n">
         <v>45810</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="E38" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I38" t="n">
         <v>17.5</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>3</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>14</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>16</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>2</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>17</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>64</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U38" t="n">
         <v>64</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Garnlav
@@ -5419,116 +5550,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 26765-2025 artfynd.xlsx", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 26765-2025 karta.png", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 26765-2025 georefererad karta.tif", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 26765-2025 FSC-klagomål.docx", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 26765-2025 FSC-klagomål mail.docx", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 26765-2025 tillsynsbegäran.docx", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 26765-2025 tillsynsbegäran mail.docx", "A 26765-2025")</f>
         <v/>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 26765-2025 prioriterade fågelarter.docx", "A 26765-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 30105-2026</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="E39" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I39" t="n">
         <v>3.1</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>3</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>14</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>16</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>53</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>50</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blanksvart spiklav
@@ -5548,116 +5679,116 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 30105-2026 artfynd.xlsx", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 30105-2026 karta.png", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 30105-2026 georefererad karta.tif", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 30105-2026 FSC-klagomål.docx", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 30105-2026 FSC-klagomål mail.docx", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 30105-2026 tillsynsbegäran.docx", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 30105-2026 tillsynsbegäran mail.docx", "A 30105-2026")</f>
         <v/>
       </c>
-      <c r="AE38">
+      <c r="AE39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 30105-2026 prioriterade fågelarter.docx", "A 30105-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>A 45113-2025</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="E40" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I40" t="n">
         <v>19.2</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>10</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M40" t="n">
         <v>5</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>15</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>5</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S40" t="n">
         <v>15</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T40" t="n">
         <v>32</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U40" t="n">
         <v>6</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Goliatmusseron
 Gräddporing
@@ -5676,107 +5807,107 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 45113-2025 artfynd.xlsx", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 45113-2025 karta.png", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 45113-2025 georefererad karta.tif", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 45113-2025 FSC-klagomål.docx", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 45113-2025 FSC-klagomål mail.docx", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 45113-2025 tillsynsbegäran.docx", "A 45113-2025")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 45113-2025 tillsynsbegäran mail.docx", "A 45113-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>A 59104-2025</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D41" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
+      <c r="E41" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
         <v>11.6</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>2</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>8</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>2</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>10</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>15</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>237</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U41" t="n">
         <v>237</v>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -5795,116 +5926,116 @@
 Orre</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 59104-2025 artfynd.xlsx", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 59104-2025 karta.png", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 59104-2025 georefererad karta.tif", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 59104-2025 FSC-klagomål.docx", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 59104-2025 FSC-klagomål mail.docx", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 59104-2025 tillsynsbegäran.docx", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 59104-2025 tillsynsbegäran mail.docx", "A 59104-2025")</f>
         <v/>
       </c>
-      <c r="AE40">
+      <c r="AE41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 59104-2025 prioriterade fågelarter.docx", "A 59104-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>A 50492-2025</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D42" s="1" t="n">
         <v>45945</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="E42" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I42" t="n">
         <v>6.2</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>2</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L42" t="n">
         <v>10</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
         <v>11</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S42" t="n">
         <v>15</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>255</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U42" t="n">
         <v>255</v>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Dropptaggsvamp
@@ -5923,116 +6054,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 50492-2025 artfynd.xlsx", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 50492-2025 karta.png", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 50492-2025 georefererad karta.tif", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 50492-2025 FSC-klagomål.docx", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 50492-2025 FSC-klagomål mail.docx", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 50492-2025 tillsynsbegäran.docx", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 50492-2025 tillsynsbegäran mail.docx", "A 50492-2025")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 50492-2025 prioriterade fågelarter.docx", "A 50492-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>A 56939-2025</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D43" s="1" t="n">
         <v>45978</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="E43" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I43" t="n">
         <v>27.1</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K43" t="n">
         <v>3</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L43" t="n">
         <v>6</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>2</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>8</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>2</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S43" t="n">
         <v>15</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T43" t="n">
         <v>249</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U43" t="n">
         <v>249</v>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -6051,120 +6182,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W42">
+      <c r="W43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 56939-2025 artfynd.xlsx", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="X42">
+      <c r="X43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 56939-2025 karta.png", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 56939-2025 georefererad karta.tif", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="Z42">
+      <c r="Z43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/knärot/A 56939-2025 karta knärot.png", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="AA42">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 56939-2025 FSC-klagomål.docx", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="AB42">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 56939-2025 FSC-klagomål mail.docx", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="AC42">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 56939-2025 tillsynsbegäran.docx", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="AD42">
+      <c r="AD43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 56939-2025 tillsynsbegäran mail.docx", "A 56939-2025")</f>
         <v/>
       </c>
-      <c r="AE42">
+      <c r="AE43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 56939-2025 prioriterade fågelarter.docx", "A 56939-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>A 34895-2026</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D44" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="E44" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I44" t="n">
         <v>18.8</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>9</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L44" t="n">
         <v>6</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
         <v>7</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S44" t="n">
         <v>15</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T44" t="n">
         <v>159</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Kolflarnlav
@@ -6183,116 +6314,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 34895-2026 artfynd.xlsx", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 34895-2026 karta.png", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 34895-2026 georefererad karta.tif", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 34895-2026 FSC-klagomål.docx", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 34895-2026 FSC-klagomål mail.docx", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 34895-2026 tillsynsbegäran.docx", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 34895-2026 tillsynsbegäran mail.docx", "A 34895-2026")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE44">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 34895-2026 prioriterade fågelarter.docx", "A 34895-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>A 31037-2023</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D45" s="1" t="n">
         <v>45113</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="E45" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ÄLVDALEN</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I45" t="n">
         <v>17.8</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>10</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>4</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>14</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S45" t="n">
         <v>14</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T45" t="n">
         <v>46</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U45" t="n">
         <v>45</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -6310,163 +6441,36 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 31037-2023 artfynd.xlsx", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 31037-2023 karta.png", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 31037-2023 georefererad karta.tif", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 31037-2023 FSC-klagomål.docx", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 31037-2023 FSC-klagomål mail.docx", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 31037-2023 tillsynsbegäran.docx", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 31037-2023 tillsynsbegäran mail.docx", "A 31037-2023")</f>
         <v/>
       </c>
-      <c r="AE44">
+      <c r="AE45">
         <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 31037-2023 prioriterade fågelarter.docx", "A 31037-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 43867-2025</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ÄLVDALEN</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J45" t="n">
-        <v>6</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>9</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>10</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>14</v>
-      </c>
-      <c r="T45" t="n">
-        <v>191</v>
-      </c>
-      <c r="U45" t="n">
-        <v>191</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Doftskinn
-Kolflarnlav
-Motaggsvamp
-Mörk kolflarnlav
-Tallticka
-Talltita
-Tretåig hackspett
-Vedflamlav
-Vedskivlav
-Plattlummer
-Spillkråka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/artfynd/A 43867-2025 artfynd.xlsx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor/A 43867-2025 karta.png", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/kartor_geotiff/A 43867-2025 georefererad karta.tif", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomål/A 43867-2025 FSC-klagomål.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/klagomålsmail/A 43867-2025 FSC-klagomål mail.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsyn/A 43867-2025 tillsynsbegäran.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/tillsynsmail/A 43867-2025 tillsynsbegäran mail.docx", "A 43867-2025")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2039/fåglar/A 43867-2025 prioriterade fågelarter.docx", "A 43867-2025")</f>
         <v/>
       </c>
     </row>
@@ -6490,7 +6494,7 @@
         <v>46107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6612,7 +6616,7 @@
         <v>44697</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6733,7 +6737,7 @@
         <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6854,7 +6858,7 @@
         <v>44532</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6971,7 +6975,7 @@
         <v>45901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7093,7 +7097,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7215,7 +7219,7 @@
         <v>46206</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7337,7 +7341,7 @@
         <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7463,7 +7467,7 @@
         <v>46108</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7589,7 +7593,7 @@
         <v>46248</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7710,7 +7714,7 @@
         <v>45407</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7835,7 +7839,7 @@
         <v>45929</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7960,7 +7964,7 @@
         <v>45834</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8085,7 +8089,7 @@
         <v>46052</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8205,7 +8209,7 @@
         <v>46058</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8329,7 +8333,7 @@
         <v>44543</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8449,7 +8453,7 @@
         <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8574,7 +8578,7 @@
         <v>45393</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8699,7 +8703,7 @@
         <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8819,7 +8823,7 @@
         <v>45159</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8943,7 +8947,7 @@
         <v>45938</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9068,7 +9072,7 @@
         <v>46267</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9192,7 +9196,7 @@
         <v>45891</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9311,7 +9315,7 @@
         <v>45909</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9430,7 +9434,7 @@
         <v>45937</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9554,7 +9558,7 @@
         <v>44846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9676,7 +9680,7 @@
         <v>45415</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9799,7 +9803,7 @@
         <v>45902</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9918,7 +9922,7 @@
         <v>45162</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10037,7 +10041,7 @@
         <v>45522</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10155,7 +10159,7 @@
         <v>45748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10273,7 +10277,7 @@
         <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10396,7 +10400,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10514,7 +10518,7 @@
         <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10637,7 +10641,7 @@
         <v>46057</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10755,7 +10759,7 @@
         <v>45895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10873,7 +10877,7 @@
         <v>46031</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10996,7 +11000,7 @@
         <v>45835</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11114,7 +11118,7 @@
         <v>45891</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11232,7 +11236,7 @@
         <v>45630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11354,7 +11358,7 @@
         <v>44519</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11472,7 +11476,7 @@
         <v>45902</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11590,7 +11594,7 @@
         <v>45362</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11708,7 +11712,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11826,7 +11830,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11948,7 +11952,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12065,7 +12069,7 @@
         <v>46274</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12187,7 +12191,7 @@
         <v>46286</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12305,7 +12309,7 @@
         <v>46142</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12427,7 +12431,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12539,7 +12543,7 @@
         <v>44923</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12659,7 +12663,7 @@
         <v>45804</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12780,7 +12784,7 @@
         <v>45966</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12896,7 +12900,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -13012,7 +13016,7 @@
         <v>45593</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13132,7 +13136,7 @@
         <v>44522</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13252,7 +13256,7 @@
         <v>46167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13372,7 +13376,7 @@
         <v>45600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13493,7 +13497,7 @@
         <v>46079</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13609,7 +13613,7 @@
         <v>46238</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13730,7 +13734,7 @@
         <v>45943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13851,7 +13855,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13967,7 +13971,7 @@
         <v>45210</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14083,7 +14087,7 @@
         <v>45834</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14199,7 +14203,7 @@
         <v>45968</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14315,7 +14319,7 @@
         <v>45987</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14431,7 +14435,7 @@
         <v>46010</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14551,7 +14555,7 @@
         <v>46057</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14666,7 +14670,7 @@
         <v>45895</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14781,7 +14785,7 @@
         <v>46238</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14901,7 +14905,7 @@
         <v>44602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -15021,7 +15025,7 @@
         <v>44828</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15132,7 +15136,7 @@
         <v>44971</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15252,7 +15256,7 @@
         <v>45365</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15370,7 +15374,7 @@
         <v>45448</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15485,7 +15489,7 @@
         <v>45804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15604,7 +15608,7 @@
         <v>45210</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15719,7 +15723,7 @@
         <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15834,7 +15838,7 @@
         <v>45841</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15949,7 +15953,7 @@
         <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16064,7 +16068,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16178,7 +16182,7 @@
         <v>45462</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16292,7 +16296,7 @@
         <v>45511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16406,7 +16410,7 @@
         <v>45902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16524,7 +16528,7 @@
         <v>45799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16638,7 +16642,7 @@
         <v>45755</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16752,7 +16756,7 @@
         <v>45173</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16870,7 +16874,7 @@
         <v>45225</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16988,7 +16992,7 @@
         <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17102,7 +17106,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17215,7 +17219,7 @@
         <v>46283</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17333,7 +17337,7 @@
         <v>46121</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17447,7 +17451,7 @@
         <v>44830</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17564,7 +17568,7 @@
         <v>45078</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17677,7 +17681,7 @@
         <v>45182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17790,7 +17794,7 @@
         <v>45537</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17903,7 +17907,7 @@
         <v>45786</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -18016,7 +18020,7 @@
         <v>45511</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18129,7 +18133,7 @@
         <v>45800</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18242,7 +18246,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18355,7 +18359,7 @@
         <v>45511</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18468,7 +18472,7 @@
         <v>45547</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18581,7 +18585,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18694,7 +18698,7 @@
         <v>45638</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18807,7 +18811,7 @@
         <v>46057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18919,7 +18923,7 @@
         <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -19032,7 +19036,7 @@
         <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19144,7 +19148,7 @@
         <v>46212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19252,7 +19256,7 @@
         <v>46212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19360,7 +19364,7 @@
         <v>46254</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19473,7 +19477,7 @@
         <v>46236</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19590,7 +19594,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19702,7 +19706,7 @@
         <v>45145</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19814,7 +19818,7 @@
         <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19926,7 +19930,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -20038,7 +20042,7 @@
         <v>45817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20150,7 +20154,7 @@
         <v>45841</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20262,7 +20266,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20378,7 +20382,7 @@
         <v>45502</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20490,7 +20494,7 @@
         <v>45985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20606,7 +20610,7 @@
         <v>45992</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20718,7 +20722,7 @@
         <v>46127</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20825,7 +20829,7 @@
         <v>46195</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20937,7 +20941,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -21049,7 +21053,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21160,7 +21164,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21266,7 +21270,7 @@
         <v>44874</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21372,7 +21376,7 @@
         <v>45404</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21478,7 +21482,7 @@
         <v>44706</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21589,7 +21593,7 @@
         <v>45817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21700,7 +21704,7 @@
         <v>45833</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21815,7 +21819,7 @@
         <v>45968</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21926,7 +21930,7 @@
         <v>45968</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -22037,7 +22041,7 @@
         <v>46121</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22152,7 +22156,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22263,7 +22267,7 @@
         <v>45895</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22373,7 +22377,7 @@
         <v>46196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22484,7 +22488,7 @@
         <v>46265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22595,7 +22599,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22706,7 +22710,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22816,7 +22820,7 @@
         <v>45575</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22926,7 +22930,7 @@
         <v>45902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -23037,7 +23041,7 @@
         <v>46106</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23152,7 +23156,7 @@
         <v>46265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23263,7 +23267,7 @@
         <v>44516</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23373,7 +23377,7 @@
         <v>44532</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23483,7 +23487,7 @@
         <v>45512</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23593,7 +23597,7 @@
         <v>44881</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23703,7 +23707,7 @@
         <v>45502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23812,7 +23816,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23922,7 +23926,7 @@
         <v>45786</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -24032,7 +24036,7 @@
         <v>45511</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24142,7 +24146,7 @@
         <v>45938</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24252,7 +24256,7 @@
         <v>45432</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24362,7 +24366,7 @@
         <v>45817</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24472,7 +24476,7 @@
         <v>45181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24577,7 +24581,7 @@
         <v>45853</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24687,7 +24691,7 @@
         <v>45153</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24796,7 +24800,7 @@
         <v>45770</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24906,7 +24910,7 @@
         <v>45572</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -25020,7 +25024,7 @@
         <v>44873</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25130,7 +25134,7 @@
         <v>45989</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25240,7 +25244,7 @@
         <v>45993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25345,7 +25349,7 @@
         <v>46127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25455,7 +25459,7 @@
         <v>46002</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25565,7 +25569,7 @@
         <v>46058</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25674,7 +25678,7 @@
         <v>46177</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25784,7 +25788,7 @@
         <v>46189</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25894,7 +25898,7 @@
         <v>45792</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25999,7 +26003,7 @@
         <v>46266</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26113,7 +26117,7 @@
         <v>46223</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26222,7 +26226,7 @@
         <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26332,7 +26336,7 @@
         <v>46233</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26437,7 +26441,7 @@
         <v>46246</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26542,7 +26546,7 @@
         <v>46248</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26652,7 +26656,7 @@
         <v>46261</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26757,7 +26761,7 @@
         <v>44629</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26871,7 +26875,7 @@
         <v>44575</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26985,7 +26989,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27095,7 +27099,7 @@
         <v>45903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27205,7 +27209,7 @@
         <v>44662</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27278,7 +27282,7 @@
         <v>44754</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27351,7 +27355,7 @@
         <v>44810</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27429,7 +27433,7 @@
         <v>44546</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27502,7 +27506,7 @@
         <v>44651</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27575,7 +27579,7 @@
         <v>44755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27648,7 +27652,7 @@
         <v>44519</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27726,7 +27730,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27804,7 +27808,7 @@
         <v>44873</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27877,7 +27881,7 @@
         <v>44817</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27955,7 +27959,7 @@
         <v>44846</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28028,7 +28032,7 @@
         <v>44504</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28106,7 +28110,7 @@
         <v>44538</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28184,7 +28188,7 @@
         <v>44865</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28262,7 +28266,7 @@
         <v>44697</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28335,7 +28339,7 @@
         <v>44539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28408,7 +28412,7 @@
         <v>44536</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28486,7 +28490,7 @@
         <v>44732</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28564,7 +28568,7 @@
         <v>44501</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28637,7 +28641,7 @@
         <v>44680</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28715,7 +28719,7 @@
         <v>44607</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28788,7 +28792,7 @@
         <v>44882</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28866,7 +28870,7 @@
         <v>44705</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28939,7 +28943,7 @@
         <v>44636</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29012,7 +29016,7 @@
         <v>44816</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29090,7 +29094,7 @@
         <v>44484</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29163,7 +29167,7 @@
         <v>44547</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29241,7 +29245,7 @@
         <v>45210</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29314,7 +29318,7 @@
         <v>45310</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29387,7 +29391,7 @@
         <v>45175</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29460,7 +29464,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29533,7 +29537,7 @@
         <v>45477</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29606,7 +29610,7 @@
         <v>45702</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29684,7 +29688,7 @@
         <v>45584</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29757,7 +29761,7 @@
         <v>44896</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29835,7 +29839,7 @@
         <v>44742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29913,7 +29917,7 @@
         <v>45584</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29986,7 +29990,7 @@
         <v>45054</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30059,7 +30063,7 @@
         <v>44651</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30137,7 +30141,7 @@
         <v>45229</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30210,7 +30214,7 @@
         <v>45113</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30288,7 +30292,7 @@
         <v>45274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30361,7 +30365,7 @@
         <v>45015</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30434,7 +30438,7 @@
         <v>45420</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30512,7 +30516,7 @@
         <v>45322</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30585,7 +30589,7 @@
         <v>45322</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30658,7 +30662,7 @@
         <v>45700</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30731,7 +30735,7 @@
         <v>44495</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30809,7 +30813,7 @@
         <v>45307</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30882,7 +30886,7 @@
         <v>45247</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30955,7 +30959,7 @@
         <v>45477</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31028,7 +31032,7 @@
         <v>45477</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31101,7 +31105,7 @@
         <v>45104</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31179,7 +31183,7 @@
         <v>45114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31252,7 +31256,7 @@
         <v>45545</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31325,7 +31329,7 @@
         <v>45124</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31398,7 +31402,7 @@
         <v>45512</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31476,7 +31480,7 @@
         <v>44963</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31549,7 +31553,7 @@
         <v>44844</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31627,7 +31631,7 @@
         <v>45299</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31700,7 +31704,7 @@
         <v>45114</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31773,7 +31777,7 @@
         <v>45209</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31846,7 +31850,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31924,7 +31928,7 @@
         <v>45534</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31997,7 +32001,7 @@
         <v>45097</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32075,7 +32079,7 @@
         <v>44844</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32148,7 +32152,7 @@
         <v>45204</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32221,7 +32225,7 @@
         <v>44894</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32294,7 +32298,7 @@
         <v>45310</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32367,7 +32371,7 @@
         <v>45310</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32440,7 +32444,7 @@
         <v>45887</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32518,7 +32522,7 @@
         <v>45335</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32591,7 +32595,7 @@
         <v>44505</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32669,7 +32673,7 @@
         <v>44558</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32742,7 +32746,7 @@
         <v>45330</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32815,7 +32819,7 @@
         <v>45488</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32888,7 +32892,7 @@
         <v>45488</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32961,7 +32965,7 @@
         <v>45898</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -33034,7 +33038,7 @@
         <v>45253</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33107,7 +33111,7 @@
         <v>45357</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33185,7 +33189,7 @@
         <v>45246</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33258,7 +33262,7 @@
         <v>45548</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33331,7 +33335,7 @@
         <v>45611</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33404,7 +33408,7 @@
         <v>44873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33477,7 +33481,7 @@
         <v>44526</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33555,7 +33559,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33628,7 +33632,7 @@
         <v>45141</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33701,7 +33705,7 @@
         <v>45911</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33774,7 +33778,7 @@
         <v>45911</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33852,7 +33856,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33925,7 +33929,7 @@
         <v>45783</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33998,7 +34002,7 @@
         <v>45783</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34071,7 +34075,7 @@
         <v>45665</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34144,7 +34148,7 @@
         <v>45034</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34217,7 +34221,7 @@
         <v>45539</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34290,7 +34294,7 @@
         <v>45348</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34363,7 +34367,7 @@
         <v>45121</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34436,7 +34440,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34514,7 +34518,7 @@
         <v>45201</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34592,7 +34596,7 @@
         <v>44916</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34665,7 +34669,7 @@
         <v>45919</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34743,7 +34747,7 @@
         <v>45432</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34816,7 +34820,7 @@
         <v>45441</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34889,7 +34893,7 @@
         <v>45588</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34962,7 +34966,7 @@
         <v>44874</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35035,7 +35039,7 @@
         <v>45491</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35108,7 +35112,7 @@
         <v>45516</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35181,7 +35185,7 @@
         <v>45120</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35254,7 +35258,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35332,7 +35336,7 @@
         <v>45572</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35410,7 +35414,7 @@
         <v>45223</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35483,7 +35487,7 @@
         <v>45204</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35556,7 +35560,7 @@
         <v>44904</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35629,7 +35633,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35707,7 +35711,7 @@
         <v>45929</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35785,7 +35789,7 @@
         <v>45114</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35858,7 +35862,7 @@
         <v>44568</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35931,7 +35935,7 @@
         <v>45212</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -36009,7 +36013,7 @@
         <v>45572</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36087,7 +36091,7 @@
         <v>45638</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36165,7 +36169,7 @@
         <v>45335</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36238,7 +36242,7 @@
         <v>45453</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36311,7 +36315,7 @@
         <v>45665</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36384,7 +36388,7 @@
         <v>45665</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36457,7 +36461,7 @@
         <v>45709</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36530,7 +36534,7 @@
         <v>45931</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36603,7 +36607,7 @@
         <v>45588</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36676,7 +36680,7 @@
         <v>44558</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36749,7 +36753,7 @@
         <v>45491</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36822,7 +36826,7 @@
         <v>45798</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36895,7 +36899,7 @@
         <v>45931</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36968,7 +36972,7 @@
         <v>44904</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37041,7 +37045,7 @@
         <v>45800</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37119,7 +37123,7 @@
         <v>44643</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37197,7 +37201,7 @@
         <v>45456</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37270,7 +37274,7 @@
         <v>45456</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37343,7 +37347,7 @@
         <v>45933</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37416,7 +37420,7 @@
         <v>45804</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37494,7 +37498,7 @@
         <v>44865</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37572,7 +37576,7 @@
         <v>45233</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37650,7 +37654,7 @@
         <v>45674</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37723,7 +37727,7 @@
         <v>45404</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37796,7 +37800,7 @@
         <v>45812</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37874,7 +37878,7 @@
         <v>45240</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37952,7 +37956,7 @@
         <v>45240</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -38030,7 +38034,7 @@
         <v>45348</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38103,7 +38107,7 @@
         <v>45350</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38181,7 +38185,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38254,7 +38258,7 @@
         <v>45950</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38327,7 +38331,7 @@
         <v>44916</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38400,7 +38404,7 @@
         <v>45322</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38473,7 +38477,7 @@
         <v>45950</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38551,7 +38555,7 @@
         <v>45950</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38629,7 +38633,7 @@
         <v>45307</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38702,7 +38706,7 @@
         <v>45210</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38780,7 +38784,7 @@
         <v>45700</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38858,7 +38862,7 @@
         <v>45952</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38936,7 +38940,7 @@
         <v>45952</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -39014,7 +39018,7 @@
         <v>45952</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39092,7 +39096,7 @@
         <v>45693</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39165,7 +39169,7 @@
         <v>45456</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39238,7 +39242,7 @@
         <v>45830</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39311,7 +39315,7 @@
         <v>45153</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39384,7 +39388,7 @@
         <v>45952</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39462,7 +39466,7 @@
         <v>45953</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39540,7 +39544,7 @@
         <v>45638</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39618,7 +39622,7 @@
         <v>45114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39691,7 +39695,7 @@
         <v>45964</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39769,7 +39773,7 @@
         <v>45114</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39847,7 +39851,7 @@
         <v>45968</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39925,7 +39929,7 @@
         <v>45322</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39998,7 +40002,7 @@
         <v>44755</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40071,7 +40075,7 @@
         <v>45159</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40149,7 +40153,7 @@
         <v>45660</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40227,7 +40231,7 @@
         <v>45303</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40300,7 +40304,7 @@
         <v>45848</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40373,7 +40377,7 @@
         <v>45848</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40446,7 +40450,7 @@
         <v>45973</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40524,7 +40528,7 @@
         <v>45722</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40602,7 +40606,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40680,7 +40684,7 @@
         <v>45973</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40758,7 +40762,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40831,7 +40835,7 @@
         <v>45201</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40909,7 +40913,7 @@
         <v>45076</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40982,7 +40986,7 @@
         <v>44978</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41055,7 +41059,7 @@
         <v>44820</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41128,7 +41132,7 @@
         <v>44859</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41206,7 +41210,7 @@
         <v>45336</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41279,7 +41283,7 @@
         <v>45863</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41357,7 +41361,7 @@
         <v>44839</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41430,7 +41434,7 @@
         <v>44526</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41508,7 +41512,7 @@
         <v>45484</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41581,7 +41585,7 @@
         <v>45415</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41654,7 +41658,7 @@
         <v>45709</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41732,7 +41736,7 @@
         <v>45874</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41810,7 +41814,7 @@
         <v>45322</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41883,7 +41887,7 @@
         <v>45310</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41956,7 +41960,7 @@
         <v>45679</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -42029,7 +42033,7 @@
         <v>45875</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42102,7 +42106,7 @@
         <v>45048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42175,7 +42179,7 @@
         <v>45980</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42248,7 +42252,7 @@
         <v>45337</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42321,7 +42325,7 @@
         <v>45110</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42399,7 +42403,7 @@
         <v>45204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42472,7 +42476,7 @@
         <v>45507</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42545,7 +42549,7 @@
         <v>45077</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42618,7 +42622,7 @@
         <v>45550</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42691,7 +42695,7 @@
         <v>44533</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42764,7 +42768,7 @@
         <v>45107</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42837,7 +42841,7 @@
         <v>45299</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42910,7 +42914,7 @@
         <v>46100</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42983,7 +42987,7 @@
         <v>45328</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43056,7 +43060,7 @@
         <v>45691</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43134,7 +43138,7 @@
         <v>45986</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43212,7 +43216,7 @@
         <v>45709</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43285,7 +43289,7 @@
         <v>46107</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43363,7 +43367,7 @@
         <v>45540</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43436,7 +43440,7 @@
         <v>45566</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43514,7 +43518,7 @@
         <v>45988</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43587,7 +43591,7 @@
         <v>45988</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43660,7 +43664,7 @@
         <v>45988</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43733,7 +43737,7 @@
         <v>45992</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43811,7 +43815,7 @@
         <v>46112</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43884,7 +43888,7 @@
         <v>46112</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43957,7 +43961,7 @@
         <v>45992</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44035,7 +44039,7 @@
         <v>45992</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44113,7 +44117,7 @@
         <v>45327</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44186,7 +44190,7 @@
         <v>45994</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44264,7 +44268,7 @@
         <v>44911</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44337,7 +44341,7 @@
         <v>45560</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44415,7 +44419,7 @@
         <v>44678</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44488,7 +44492,7 @@
         <v>44910</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44561,7 +44565,7 @@
         <v>45996</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44634,7 +44638,7 @@
         <v>46127</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44707,7 +44711,7 @@
         <v>46001</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44780,7 +44784,7 @@
         <v>46127</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44853,7 +44857,7 @@
         <v>44904</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44926,7 +44930,7 @@
         <v>45247</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44999,7 +45003,7 @@
         <v>46006</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45072,7 +45076,7 @@
         <v>46003</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45145,7 +45149,7 @@
         <v>45246</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45218,7 +45222,7 @@
         <v>45072</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45296,7 +45300,7 @@
         <v>45175</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45369,7 +45373,7 @@
         <v>44755</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45447,7 +45451,7 @@
         <v>44496</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45525,7 +45529,7 @@
         <v>46009</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45598,7 +45602,7 @@
         <v>46013</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45671,7 +45675,7 @@
         <v>46014</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45744,7 +45748,7 @@
         <v>45597</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45817,7 +45821,7 @@
         <v>45356</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45890,7 +45894,7 @@
         <v>45901</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45963,7 +45967,7 @@
         <v>46030</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46036,7 +46040,7 @@
         <v>46029</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46109,7 +46113,7 @@
         <v>46029</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46182,7 +46186,7 @@
         <v>46029</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46255,7 +46259,7 @@
         <v>45106</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46328,7 +46332,7 @@
         <v>46035</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46406,7 +46410,7 @@
         <v>46038</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46479,7 +46483,7 @@
         <v>46038</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46552,7 +46556,7 @@
         <v>46038</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46625,7 +46629,7 @@
         <v>46038</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46698,7 +46702,7 @@
         <v>46038</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46771,7 +46775,7 @@
         <v>46038</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46844,7 +46848,7 @@
         <v>46038</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46917,7 +46921,7 @@
         <v>46031</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46995,7 +46999,7 @@
         <v>46038</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47068,7 +47072,7 @@
         <v>46041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47141,7 +47145,7 @@
         <v>46041</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47214,7 +47218,7 @@
         <v>46042</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47287,7 +47291,7 @@
         <v>46043</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47360,7 +47364,7 @@
         <v>45630</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47433,7 +47437,7 @@
         <v>46044</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47506,7 +47510,7 @@
         <v>46043</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47579,7 +47583,7 @@
         <v>46043</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47652,7 +47656,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47725,7 +47729,7 @@
         <v>46043</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47798,7 +47802,7 @@
         <v>46079</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47871,7 +47875,7 @@
         <v>45770</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47949,7 +47953,7 @@
         <v>44888</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48022,7 +48026,7 @@
         <v>45485</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48095,7 +48099,7 @@
         <v>44873</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48168,7 +48172,7 @@
         <v>45254</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48241,7 +48245,7 @@
         <v>45589</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48314,7 +48318,7 @@
         <v>46057</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48387,7 +48391,7 @@
         <v>46062</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48460,7 +48464,7 @@
         <v>46062</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48533,7 +48537,7 @@
         <v>46062</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48606,7 +48610,7 @@
         <v>46062</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48679,7 +48683,7 @@
         <v>46043</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48752,7 +48756,7 @@
         <v>46062</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48825,7 +48829,7 @@
         <v>46148</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48898,7 +48902,7 @@
         <v>46148</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48971,7 +48975,7 @@
         <v>46148</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49044,7 +49048,7 @@
         <v>46066</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49117,7 +49121,7 @@
         <v>46149</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49195,7 +49199,7 @@
         <v>46149</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49273,7 +49277,7 @@
         <v>46149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49351,7 +49355,7 @@
         <v>46071</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49424,7 +49428,7 @@
         <v>46071</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49497,7 +49501,7 @@
         <v>44754</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49570,7 +49574,7 @@
         <v>46154</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49643,7 +49647,7 @@
         <v>46153</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49716,7 +49720,7 @@
         <v>46073</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49789,7 +49793,7 @@
         <v>46078</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49862,7 +49866,7 @@
         <v>46085</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49935,7 +49939,7 @@
         <v>46168</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50013,7 +50017,7 @@
         <v>45925</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50086,7 +50090,7 @@
         <v>46174</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50159,7 +50163,7 @@
         <v>46052</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50232,7 +50236,7 @@
         <v>46174</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50305,7 +50309,7 @@
         <v>46174</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50378,7 +50382,7 @@
         <v>46174</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50451,7 +50455,7 @@
         <v>46030</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50524,7 +50528,7 @@
         <v>46177</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50597,7 +50601,7 @@
         <v>46211</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50670,7 +50674,7 @@
         <v>46083</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50743,7 +50747,7 @@
         <v>46261</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50816,7 +50820,7 @@
         <v>45537</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50889,7 +50893,7 @@
         <v>46268</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50962,7 +50966,7 @@
         <v>46269</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51035,7 +51039,7 @@
         <v>46269</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51108,7 +51112,7 @@
         <v>46041</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51181,7 +51185,7 @@
         <v>46231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51259,7 +51263,7 @@
         <v>46231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51337,7 +51341,7 @@
         <v>46276</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51415,7 +51419,7 @@
         <v>46233</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51493,7 +51497,7 @@
         <v>46236</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51571,7 +51575,7 @@
         <v>46233</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51649,7 +51653,7 @@
         <v>46233</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51727,7 +51731,7 @@
         <v>46239</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51805,7 +51809,7 @@
         <v>46286</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51883,7 +51887,7 @@
         <v>46112</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51956,7 +51960,7 @@
         <v>46246</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52029,7 +52033,7 @@
         <v>46288</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52102,7 +52106,7 @@
         <v>46288</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52175,7 +52179,7 @@
         <v>46246</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52248,7 +52252,7 @@
         <v>46246</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52321,7 +52325,7 @@
         <v>45575</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52394,7 +52398,7 @@
         <v>46246</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52467,7 +52471,7 @@
         <v>46294</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52540,7 +52544,7 @@
         <v>46296</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52613,7 +52617,7 @@
         <v>46296</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52686,7 +52690,7 @@
         <v>46296</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52764,7 +52768,7 @@
         <v>46252</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52837,7 +52841,7 @@
         <v>45926</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52943,7 +52947,7 @@
         <v>45964</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53016,7 +53020,7 @@
         <v>46258</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53089,7 +53093,7 @@
         <v>46258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53162,7 +53166,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53235,7 +53239,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53308,7 +53312,7 @@
         <v>46259</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53386,7 +53390,7 @@
         <v>46261</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53464,7 +53468,7 @@
         <v>46260</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53537,7 +53541,7 @@
         <v>46262</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53610,7 +53614,7 @@
         <v>46261</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53683,7 +53687,7 @@
         <v>46262</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53756,7 +53760,7 @@
         <v>46262</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53829,7 +53833,7 @@
         <v>46262</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53902,7 +53906,7 @@
         <v>44083</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53980,7 +53984,7 @@
         <v>44637</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54058,7 +54062,7 @@
         <v>44692</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54136,7 +54140,7 @@
         <v>44692</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54214,7 +54218,7 @@
         <v>44692</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54292,7 +54296,7 @@
         <v>44715</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54370,7 +54374,7 @@
         <v>44698</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54448,7 +54452,7 @@
         <v>44602</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54526,7 +54530,7 @@
         <v>44602</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54604,7 +54608,7 @@
         <v>44602</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54682,7 +54686,7 @@
         <v>44662</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54755,7 +54759,7 @@
         <v>44708</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54833,7 +54837,7 @@
         <v>45357</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54911,7 +54915,7 @@
         <v>45355</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54989,7 +54993,7 @@
         <v>45356</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55067,7 +55071,7 @@
         <v>45684</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55145,7 +55149,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55223,7 +55227,7 @@
         <v>45359</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55301,7 +55305,7 @@
         <v>45359</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55379,7 +55383,7 @@
         <v>45355</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55457,7 +55461,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55535,7 +55539,7 @@
         <v>45684</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55613,7 +55617,7 @@
         <v>44806</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55686,7 +55690,7 @@
         <v>45356</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55764,7 +55768,7 @@
         <v>45359</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55842,7 +55846,7 @@
         <v>45357</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55920,7 +55924,7 @@
         <v>45357</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55998,7 +56002,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56076,7 +56080,7 @@
         <v>45356</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56154,7 +56158,7 @@
         <v>45355</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56232,7 +56236,7 @@
         <v>45684</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56310,7 +56314,7 @@
         <v>45715</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56383,7 +56387,7 @@
         <v>45684</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56461,7 +56465,7 @@
         <v>45713</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56539,7 +56543,7 @@
         <v>45714</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56617,7 +56621,7 @@
         <v>45758</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56695,7 +56699,7 @@
         <v>45757</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56773,7 +56777,7 @@
         <v>45757</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56851,7 +56855,7 @@
         <v>45757</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56929,7 +56933,7 @@
         <v>45757</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -57007,7 +57011,7 @@
         <v>45575</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57080,7 +57084,7 @@
         <v>45684</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57158,7 +57162,7 @@
         <v>46089</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57236,7 +57240,7 @@
         <v>46089</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57314,7 +57318,7 @@
         <v>46104</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57392,7 +57396,7 @@
         <v>46104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57470,7 +57474,7 @@
         <v>46105</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57548,7 +57552,7 @@
         <v>46104</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57626,7 +57630,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57704,7 +57708,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57782,7 +57786,7 @@
         <v>46150</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>46048</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46255</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45901</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46259</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>46252</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45700</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45110</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45502</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45825</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45926</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45945</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46301</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>45278</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>46267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46238</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45118</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>45868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44697</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45901</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>46108</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45407</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>46052</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>46058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45938</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44543</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45393</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45159</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>45909</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46267</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45162</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45748</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45415</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45522</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45891</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45362</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45630</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44519</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>46274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>46142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>46286</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44522</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>44923</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>46238</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>46079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45968</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45987</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46010</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>46057</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45895</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46238</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44828</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>46134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45448</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45210</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45365</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45841</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45173</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45902</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45755</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45432</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>46283</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45462</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45799</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45182</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45537</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45547</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45937</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46057</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>44830</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45511</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45511</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45153</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46236</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46254</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45786</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45800</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45426</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44830</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45502</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>46195</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46127</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45343</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45810</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45817</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44706</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45404</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>46177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>46196</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46121</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>46286</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44874</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45575</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46106</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>46265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44516</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44532</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45432</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45512</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45989</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45993</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46002</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>46177</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46058</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>46189</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44873</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45792</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>46223</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46248</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45786</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>46261</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45817</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45770</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44575</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44662</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>44810</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44754</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44755</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44519</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44817</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>44873</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44504</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44538</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>44865</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44697</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>44501</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44705</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44732</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44536</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44680</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44607</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>44882</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44636</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44547</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45456</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45534</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45054</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45097</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44558</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>44526</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45307</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45247</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45246</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45357</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45491</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45477</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45477</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45335</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>44526</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>44755</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45693</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45548</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45679</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45015</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45597</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45322</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45322</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45322</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45335</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44873</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45310</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45310</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45299</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45566</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45175</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44505</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45665</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45201</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45310</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45336</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45299</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45491</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45233</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45901</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45630</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45700</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45722</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45560</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44911</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45512</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45159</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46037</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45589</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>45898</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>46079</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>46043</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45484</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45477</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45911</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45322</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45919</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45929</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46149</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45926</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46148</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46148</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46149</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45931</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45931</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45933</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46153</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45420</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45950</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45950</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45950</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46154</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45953</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45638</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>44754</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45952</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45952</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45254</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>45952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45709</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45356</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44904</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45212</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45968</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45209</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45973</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45974</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45141</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>44844</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45980</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>44896</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45077</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45986</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>44678</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45992</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>46168</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45076</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45994</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45485</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>45996</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>45246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>46001</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>46052</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45124</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>46003</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>44859</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>46006</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>46009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>46174</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>46174</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45550</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>46014</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45925</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46029</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>44558</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>44495</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>46030</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44651</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>46035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>46031</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>46041</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>46041</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>46038</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>46038</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>46038</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>45456</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45456</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46038</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>46038</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>46038</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>46038</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>46038</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>46043</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>46043</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>46177</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>46042</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45110</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45770</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>46044</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46057</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45072</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46062</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>46062</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46062</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>46062</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45665</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45700</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45584</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46066</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44755</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>44873</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46071</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>46071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>46073</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45240</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45240</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>46085</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44844</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>46100</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45588</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45204</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45507</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>46107</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46112</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46112</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45328</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>44978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>46127</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>46127</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44874</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45104</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45113</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45114</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45540</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45404</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45660</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>46211</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45120</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>46083</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45201</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45537</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>44904</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45253</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>46041</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>46231</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>46231</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45114</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>44916</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45611</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>46276</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>46233</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>46233</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>46236</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>46233</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45337</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>44894</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45204</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>44963</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>46239</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>46286</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45229</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44533</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45114</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>46246</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>46246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45303</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>46246</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44916</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>46112</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>46246</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45330</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45702</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45516</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>45584</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45488</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45175</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>46294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>44643</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>45572</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44910</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45709</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45709</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>46296</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>46296</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46296</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46252</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>44742</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45034</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45348</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>45310</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44496</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>46258</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>46258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45783</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45783</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>46258</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45539</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45785</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45432</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45441</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45121</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>45348</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45964</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51223,7 +51223,7 @@
         <v>46260</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>46259</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45223</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>46258</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>46262</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45588</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46261</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45453</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45926</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>46262</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46262</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>46261</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46262</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45798</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45800</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>44865</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45804</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45674</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>45812</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52673,7 +52673,7 @@
         <v>45350</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46269</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45322</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>46261</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>46268</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>46269</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>45830</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53189,7 +53189,7 @@
         <v>45848</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45848</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45863</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53413,7 +53413,7 @@
         <v>45415</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45874</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45875</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45114</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>44637</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>44083</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45357</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44692</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>44692</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45355</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>45356</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45684</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>44692</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>44715</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45359</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45359</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>44698</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54802,7 +54802,7 @@
         <v>45355</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>44602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45355</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45684</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>44806</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55187,7 +55187,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45359</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>44602</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45357</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45357</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>44602</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45356</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45356</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>44662</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>45355</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>44708</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45684</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45715</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45684</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45713</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45714</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>45757</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45757</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>45757</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45757</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>45758</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>45575</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45684</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>46089</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>46089</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46104</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>46104</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57278,7 +57278,7 @@
         <v>46104</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>46104</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>46104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46105</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>46150</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45173</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>46048</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46287</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46255</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45901</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46259</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>46252</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45700</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45110</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45502</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45833</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45825</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45926</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45945</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46301</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>45278</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>46267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46238</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45118</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>45868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44697</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45901</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>46108</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45407</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>46052</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>46058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45973</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45938</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44543</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45393</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45159</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>45909</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46267</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45162</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45748</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45415</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45522</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45891</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45362</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45630</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44519</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>46274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>46142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>46286</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44522</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>44923</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>46238</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>46079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45968</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45987</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46010</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>46057</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45895</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46238</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44828</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>46134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45448</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45210</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45365</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45841</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45173</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45902</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>46202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45755</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45432</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>46283</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45462</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45799</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45182</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45537</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45547</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45937</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46057</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>44830</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45511</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45511</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45153</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46236</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46254</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45786</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45800</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45426</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44830</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45502</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>46195</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46127</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45343</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45810</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45817</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44706</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45404</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>46177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>46196</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46121</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>46286</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44874</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45575</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46106</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>46265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44516</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44532</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45432</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45512</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45989</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45993</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46002</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>46177</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46058</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>46189</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44873</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45792</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>46223</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46248</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45786</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>46261</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45817</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45770</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44575</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44662</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>44810</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44754</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44755</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44519</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44817</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>44873</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44504</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44846</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44538</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>44865</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44697</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>44501</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44705</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44732</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44536</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44680</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44607</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>44882</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44636</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44547</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45456</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45534</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45054</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45097</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44558</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>44526</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45307</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45247</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45246</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45357</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45491</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45477</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45477</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45335</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>44526</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>44755</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45693</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45548</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45679</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45015</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45597</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45322</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45322</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45322</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45335</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44873</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45310</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45310</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45299</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45566</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45175</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44505</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45665</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45201</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45310</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45336</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45299</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45491</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45233</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45901</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45630</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45700</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45722</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45560</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44911</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45512</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45159</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46037</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45589</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>45898</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>46079</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>46043</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45484</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45477</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45911</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45322</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45919</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45929</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46149</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45926</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46148</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46148</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46149</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45931</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45931</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45933</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46153</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45420</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45950</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45950</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45950</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46154</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45953</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45638</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>44754</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45952</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45952</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45254</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>45952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45709</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45356</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44904</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45212</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45968</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45209</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45973</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45974</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45141</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>44844</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45980</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>44896</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45077</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45986</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>44678</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45992</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>46168</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45076</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45994</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45485</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>45996</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>45246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>46001</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>46052</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45124</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>46003</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>44859</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>46006</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>46009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>46174</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>46174</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45550</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>46014</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45925</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46029</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>44558</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>44495</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>46030</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44651</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>46035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>46031</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>46041</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>46041</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>46038</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>46038</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>46038</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>45456</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45456</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46038</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>46038</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>46038</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>46038</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>46038</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>46043</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>46043</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>46177</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>46042</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45110</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45770</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>46044</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46057</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45072</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46062</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>46062</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46062</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>46062</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45665</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45700</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45584</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46066</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44755</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>44873</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46071</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>46071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>46073</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45240</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45240</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>46085</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44844</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>46100</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45588</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45204</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45507</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>46107</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46112</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46112</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45328</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>44978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>46127</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>46127</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44874</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45104</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45113</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45114</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45540</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45404</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45660</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>46211</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45120</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>46083</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45201</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45537</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>44904</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45253</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>46041</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>46231</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>46231</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45114</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>44916</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45611</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>46276</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>46233</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>46233</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>46236</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>46233</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45337</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>44894</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45204</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>44963</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>46239</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>46286</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45229</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44533</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45114</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>46246</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>46246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45303</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>46246</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44916</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>46112</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>46246</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45330</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45702</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45516</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>45584</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45488</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45175</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>46294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>44643</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>45572</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44910</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45709</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45709</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>46296</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>46296</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46296</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46252</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>44742</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45034</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45348</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>45310</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44496</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>46258</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>46258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45783</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45783</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>46258</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45539</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45785</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45432</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45441</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45121</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>45348</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45964</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51223,7 +51223,7 @@
         <v>46260</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>46259</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45223</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>46258</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>46262</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45588</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46261</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45453</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45926</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>46262</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46262</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>46261</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46262</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45798</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45800</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>44865</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45804</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45674</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>45812</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52673,7 +52673,7 @@
         <v>45350</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46269</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45322</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>46261</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>46268</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>46269</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>45830</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53189,7 +53189,7 @@
         <v>45848</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45848</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45863</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53413,7 +53413,7 @@
         <v>45415</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45874</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45875</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45114</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>44637</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>44083</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45357</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44692</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>44692</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45355</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>45356</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45684</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>44692</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>44715</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45359</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45359</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>44698</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54802,7 +54802,7 @@
         <v>45355</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>44602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45355</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45684</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>44806</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55187,7 +55187,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45359</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>44602</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45357</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45357</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>44602</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45356</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45356</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>44662</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>45355</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>44708</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45684</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45715</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45684</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45713</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45714</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>45757</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45757</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>45757</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45757</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>45758</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>45575</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45684</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>46089</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>46089</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46104</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>46104</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57278,7 +57278,7 @@
         <v>46104</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>46104</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>46104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46105</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>46150</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46048</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45173</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>46287</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>46301</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45901</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>46259</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>46252</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>45700</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45833</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45502</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45825</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45110</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45926</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45973</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45945</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46238</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45278</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45118</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45988</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44697</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>46057</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46108</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45407</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45918</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45834</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44543</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45393</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>46052</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>46058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45938</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45159</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45909</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>46267</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45891</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45415</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45891</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45835</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45792</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46031</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45522</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45630</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>46286</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>46142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>46296</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45362</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>46274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45966</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44923</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46079</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45968</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45987</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>46010</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46057</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45210</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44828</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45365</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45841</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46134</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45210</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45462</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46202</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>46283</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45511</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45173</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45432</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44830</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45937</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>46202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46212</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>46212</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45786</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>46254</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45537</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46236</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45511</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45078</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45511</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45153</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45547</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45426</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45985</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45992</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45343</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45841</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>46127</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45502</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>46177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45968</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46196</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45404</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46286</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45817</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45833</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44874</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>46121</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45575</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45895</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>46318</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44706</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46106</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>44516</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45911</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46177</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45512</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45792</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45989</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46223</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46231</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>46233</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45786</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>46246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44881</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46058</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46248</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45853</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45770</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45572</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>46261</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45511</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45153</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44873</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45432</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45181</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44629</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44692</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45359</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45684</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45713</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44662</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44754</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44810</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44546</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44651</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44755</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44519</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44873</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44817</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44504</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44846</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44538</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44865</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44697</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>44732</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>44539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44536</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44680</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44607</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44636</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45887</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45175</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44755</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>44496</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44844</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45356</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45919</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45310</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>46168</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45926</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45929</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45931</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45925</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45485</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>44873</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45933</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45254</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45702</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>46052</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46174</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>46030</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>46177</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45229</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45420</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45477</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45477</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45477</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45114</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45545</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45950</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45584</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45950</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45950</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45950</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>45952</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45584</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45952</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45953</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>44651</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45512</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45322</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45322</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45964</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45124</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>45299</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45209</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45534</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45986</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45988</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45988</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45988</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45246</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45992</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45992</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45097</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45996</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>46083</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45611</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>46001</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>44844</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>45537</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>46006</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>46041</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46003</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46231</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>45783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46231</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>46233</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45785</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46236</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46233</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>46009</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>46013</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>46014</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45432</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>46233</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45441</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>44894</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>46030</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>46239</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>46029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45223</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>46029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>46029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>46286</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>46035</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46038</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>46038</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46038</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46038</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>46038</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>46038</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>46038</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45453</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>46031</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>46038</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>46041</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>46041</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>46042</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>46043</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45798</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>46044</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>46043</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46112</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>46043</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>46043</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45770</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46288</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46288</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45800</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45804</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>44865</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46246</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45674</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46057</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>46246</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>46294</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46062</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46062</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>46062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45812</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46062</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45350</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>46066</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45322</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46071</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>46296</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46296</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46073</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>46078</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45830</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46085</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45330</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46100</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45488</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45488</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45848</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45848</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46258</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>46258</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>46107</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>46259</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>46112</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45357</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45863</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>46261</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45415</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45548</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>46260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>45874</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>46261</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>46127</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46262</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>44873</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46262</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45114</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>44526</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45646</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45665</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46262</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>46261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45901</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>44874</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>46269</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45491</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45516</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>46268</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46269</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45572</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44904</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45630</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45212</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45335</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46037</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>46079</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45709</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46318</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45589</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>46318</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>46276</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>46318</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44904</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45926</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46148</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>46148</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46148</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45233</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>46149</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>46149</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>46149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44754</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46154</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>46153</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45348</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>44916</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45307</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45638</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44755</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45660</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45722</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45722</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45201</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44978</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>44820</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>44859</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>45709</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45679</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45337</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45110</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>44533</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45107</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45709</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>44911</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49788,7 +49788,7 @@
         <v>45175</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45253</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45015</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>44495</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>44963</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45113</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45310</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>45310</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45335</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>44505</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>44558</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45141</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45034</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45201</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>44916</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>45588</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45120</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>45114</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>44568</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45638</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45665</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>45665</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>44558</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45491</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44643</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>45456</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45456</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45404</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>45240</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45240</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45210</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45700</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45693</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>45456</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45322</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45303</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>45336</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         <v>44839</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44526</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45484</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>45322</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45310</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45204</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45507</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45077</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45550</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>45299</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45328</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45691</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>45540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45566</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45560</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>44678</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>44910</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>44904</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45247</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>44083</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>44637</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>44692</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>44692</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>44715</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44698</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44602</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>44602</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44602</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>44662</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>44708</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -55174,7 +55174,7 @@
         <v>45357</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45355</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         <v>45684</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45356</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45359</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55642,7 +55642,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45355</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>45684</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>44806</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45356</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45359</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45357</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45357</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>45356</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45356</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45355</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>45684</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45715</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45684</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45714</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>45758</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56880,7 +56880,7 @@
         <v>45757</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45757</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>45757</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -57114,7 +57114,7 @@
         <v>45757</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45575</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45684</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>46089</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>46089</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>46104</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>46105</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>46104</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>46150</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt ÄLVDALEN.xlsx
+++ b/Översikt ÄLVDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>46058</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46048</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45173</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>46287</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>46301</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45901</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>46259</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>46252</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>45700</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45833</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45502</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45825</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45110</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45926</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45973</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45945</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46238</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45278</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45118</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45919</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45988</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44697</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>46057</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46108</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45407</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45918</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45834</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44543</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45393</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>46052</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>46058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45938</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45159</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45909</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>46267</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45891</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45415</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45891</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45835</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45792</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46031</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45522</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45630</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>46286</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>46142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>46296</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45362</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>46274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45966</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44923</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46079</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45968</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45987</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>46010</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46057</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45210</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44828</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45365</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45841</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46134</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45210</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45462</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46202</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45225</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>46283</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45511</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45173</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45432</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44830</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45937</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>46202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46212</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>46212</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45786</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>46254</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45537</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>46135</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46236</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45511</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45078</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45511</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45153</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45547</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45426</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45985</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45992</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45343</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45841</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>46127</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45502</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44525</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>46177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45968</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46196</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45404</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46286</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45817</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45833</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44874</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>46121</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46265</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45575</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45895</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>46318</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44706</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46106</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>44516</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45911</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46177</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45512</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45792</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45989</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46223</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46231</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>46233</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45786</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>46246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44881</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46058</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46248</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45853</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45770</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45572</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>46261</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45511</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45153</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44873</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45432</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45181</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44629</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44692</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45359</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45684</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45713</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44662</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44754</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44810</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44546</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44651</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44755</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44519</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44873</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44817</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44504</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44846</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44538</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44865</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44697</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>44732</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>44539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44536</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44680</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44607</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44636</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45887</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45175</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44755</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>44496</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44844</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45356</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45919</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45310</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>46168</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45926</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45929</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45931</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45925</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45485</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>44873</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45933</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45254</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45702</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>46052</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46174</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>46030</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>46177</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45229</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45420</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45477</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45477</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45477</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45114</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45545</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45950</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45584</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45950</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45950</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45950</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>45952</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45584</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45952</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45953</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>44651</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45512</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45322</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45322</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45307</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45964</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45124</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>45299</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45209</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45534</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45986</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45988</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45988</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45988</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45246</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45992</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45992</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45097</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45996</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>46083</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45611</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>46001</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>44844</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>45537</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>46006</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>46041</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46003</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46231</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>45783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46231</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>46233</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45785</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46236</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46233</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>46009</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>46013</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>46014</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45432</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>46233</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45441</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>44894</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>46030</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>46239</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>46029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45223</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>46029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>46029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>46286</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>46035</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46038</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>46038</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46038</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46038</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>46038</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>46038</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>46038</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45453</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>46031</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>46038</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>46041</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>46041</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>46042</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>46043</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45798</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>46044</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>46043</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46112</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>46043</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>46043</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45770</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46288</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46288</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45800</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45804</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>44865</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46246</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45674</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46057</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>46246</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>46294</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46062</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46062</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>46062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45812</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46062</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45350</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>46066</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45322</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46071</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>46296</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46296</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46073</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>46078</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45830</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46085</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45330</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46100</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45488</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45488</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45848</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45848</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46258</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>46258</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>46107</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>46259</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>46112</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45357</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45863</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>46261</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45415</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45548</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>46260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>45874</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>46261</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>46127</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46262</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>44873</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46262</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45114</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>44526</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45646</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45665</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46262</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>46261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45901</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>44874</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>46269</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45491</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45516</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>46268</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46269</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45572</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44904</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45630</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45212</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45335</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46037</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>46079</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45709</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46318</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45589</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>46318</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>46276</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>46318</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44904</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45926</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46148</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>46148</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46148</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45233</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>46149</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>46149</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>46149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44754</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46154</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>46153</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45348</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>44916</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45307</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45638</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44755</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45660</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45722</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45722</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45201</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44978</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>44820</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>44859</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>45709</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45679</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45337</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45110</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>44533</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45107</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45709</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>44911</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49788,7 +49788,7 @@
         <v>45175</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45253</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45015</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>44495</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>44963</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45113</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45310</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>45310</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45335</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>44505</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>44558</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45141</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45034</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45201</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>44916</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>45588</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45120</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>45114</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>44568</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45638</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45665</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>45665</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>44558</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45491</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44643</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>45456</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45456</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45404</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>45240</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45240</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45210</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45700</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45693</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>45456</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45322</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45303</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>45336</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         <v>44839</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44526</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45484</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>45322</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45310</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45204</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45507</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45077</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45550</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>45299</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45328</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45691</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>45540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45566</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45327</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45560</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>44678</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>44910</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>44904</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45247</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>44083</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>44637</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>44692</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>44692</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>44715</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44698</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44602</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>44602</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44602</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>44662</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>44708</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -55174,7 +55174,7 @@
         <v>45357</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45355</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         <v>45684</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45356</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45359</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55642,7 +55642,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45355</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>45684</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>44806</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45356</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45359</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45357</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45357</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>45356</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45356</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45355</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>45684</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45715</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45684</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45714</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>45758</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56880,7 +56880,7 @@
         <v>45757</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45757</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>45757</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -57114,7 +57114,7 @@
         <v>45757</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45575</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45684</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>46089</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>46089</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>46104</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>46105</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>46104</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>46150</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
